--- a/data/database/shopgraph_purchase_history copy.xlsx
+++ b/data/database/shopgraph_purchase_history copy.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Manager" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imported Receipts" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP w1_Aug 26" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$S$122</definedName>
@@ -34,7 +35,7 @@
     <numFmt numFmtId="169" formatCode="mmm yyyy"/>
     <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,6 +124,14 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="40">
@@ -364,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -550,6 +559,9 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,7 +640,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
   <chart>
     <title>
       <tx>
@@ -3188,9 +3199,159 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Budget Burndown</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'BP w1_Aug 26'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'BP w1_Aug 26'!$L$2:$L$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP w1_Aug 26'!$M$2:$M$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'BP w1_Aug 26'!N1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'BP w1_Aug 26'!$L$2:$L$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP w1_Aug 26'!$N$2:$N$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Remaining Budget</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3597,7 +3758,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3780,7 +3940,6 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -4136,7 +4295,6 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -4389,7 +4547,6 @@
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -4629,7 +4786,6 @@
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -6381,6 +6537,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -19901,8 +20084,8 @@
     <mergeCell ref="Y59:AG62"/>
     <mergeCell ref="S112:V112"/>
     <mergeCell ref="Y142:AG142"/>
+    <mergeCell ref="S146:V146"/>
     <mergeCell ref="S317:V317"/>
-    <mergeCell ref="S146:V146"/>
     <mergeCell ref="Y114:AG114"/>
     <mergeCell ref="S99:V99"/>
     <mergeCell ref="S151:V151"/>
@@ -24672,4 +24855,288 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" style="41" min="1" max="1"/>
+    <col width="48" customWidth="1" style="41" min="2" max="2"/>
+    <col width="22" customWidth="1" style="41" min="12" max="12"/>
+    <col width="22" customWidth="1" style="41" min="13" max="13"/>
+    <col width="22" customWidth="1" style="41" min="14" max="14"/>
+    <col width="22" customWidth="1" style="41" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="89" t="inlineStr">
+        <is>
+          <t>w1_Aug</t>
+        </is>
+      </c>
+      <c r="L1" s="85" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="M1" s="85" t="inlineStr">
+        <is>
+          <t>Ideal Remaining Budget</t>
+        </is>
+      </c>
+      <c r="N1" s="85" t="inlineStr">
+        <is>
+          <t>Actual Remaining Budget</t>
+        </is>
+      </c>
+      <c r="O1" s="85" t="inlineStr">
+        <is>
+          <t>Cumulative Spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="L2" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="M2" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="N2" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="O2" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="90" t="inlineStr">
+        <is>
+          <t>Budget Plan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>w1_Aug</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M3" s="87" t="n">
+        <v>233.3333333333333</v>
+      </c>
+      <c r="N3" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="O3" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="90" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M4" s="87" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="N4" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="O4" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="90" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="M5" s="87" t="n">
+        <v>140</v>
+      </c>
+      <c r="N5" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="O5" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="90" t="inlineStr">
+        <is>
+          <t>Category Scope</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>All Categories</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M6" s="87" t="n">
+        <v>93.33333333333334</v>
+      </c>
+      <c r="N6" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="O6" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="90" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>All Categories</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="M7" s="87" t="n">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="N7" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="O7" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="90" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="B8" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="M8" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="87" t="n">
+        <v>280</v>
+      </c>
+      <c r="O8" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>Total Spent</t>
+        </is>
+      </c>
+      <c r="B9" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="90" t="inlineStr">
+        <is>
+          <t>Remaining Budget</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="90" t="inlineStr">
+        <is>
+          <t>Relevant Date</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="90" t="inlineStr">
+        <is>
+          <t>Ideal Spending Through Relevant Date</t>
+        </is>
+      </c>
+      <c r="B12" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="90" t="inlineStr">
+        <is>
+          <t>Actual Spending Through Relevant Date</t>
+        </is>
+      </c>
+      <c r="B13" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="90" t="inlineStr">
+        <is>
+          <t>Ahead / Behind Budget</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>On pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="91" t="inlineStr">
+        <is>
+          <t>Budget Burndown</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="40" t="inlineStr">
+        <is>
+          <t>Interpretation: Actual Remaining above Ideal Remaining means spending is running below the planned burn rate. Below the ideal line means spending is running above the planned burn rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A47:H49"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/database/shopgraph_purchase_history copy.xlsx
+++ b/data/database/shopgraph_purchase_history copy.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP 9_26w1 26" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$S$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$S$167</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Category Manager'!$A$1:$P$64</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -26,13 +26,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm"/>
     <numFmt numFmtId="166" formatCode="mmm\ yyyy"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="169" formatCode="mm/dd/yyyy hh:mm"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -669,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -967,6 +969,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3425,7 +3429,6 @@
 
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -4273,7 +4276,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -11389,108 +11392,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S147"/>
+  <dimension ref="A1:S167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="84" min="1" max="1"/>
     <col width="3" customWidth="1" style="84" min="2" max="2"/>
     <col width="18" customWidth="1" style="84" min="3" max="4"/>
+    <col width="18" customWidth="1" style="84" min="4" max="4"/>
     <col width="34" customWidth="1" style="84" min="5" max="5"/>
     <col width="14" customWidth="1" style="84" min="6" max="6"/>
     <col width="16" customWidth="1" style="84" min="7" max="7"/>
     <col width="28" bestFit="1" customWidth="1" style="84" min="8" max="8"/>
     <col width="22" customWidth="1" style="84" min="9" max="9"/>
     <col width="14" customWidth="1" style="84" min="10" max="19"/>
+    <col width="14" customWidth="1" style="84" min="11" max="11"/>
+    <col width="14" customWidth="1" style="84" min="12" max="12"/>
+    <col width="14" customWidth="1" style="84" min="13" max="13"/>
+    <col width="14" customWidth="1" style="84" min="14" max="14"/>
+    <col width="14" customWidth="1" style="84" min="15" max="15"/>
+    <col width="14" customWidth="1" style="84" min="16" max="16"/>
+    <col width="14" customWidth="1" style="84" min="17" max="17"/>
+    <col width="14" customWidth="1" style="84" min="18" max="18"/>
+    <col width="14" customWidth="1" style="84" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="107" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B1" s="69" t="n"/>
-      <c r="C1" s="69" t="inlineStr">
+      <c r="B1" s="107" t="n"/>
+      <c r="C1" s="107" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="D1" s="69" t="inlineStr">
+      <c r="D1" s="107" t="inlineStr">
         <is>
           <t>Six-Digit SKU</t>
         </is>
       </c>
-      <c r="E1" s="69" t="inlineStr">
+      <c r="E1" s="107" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="F1" s="69" t="inlineStr">
+      <c r="F1" s="107" t="inlineStr">
         <is>
           <t>Tax Code</t>
         </is>
       </c>
-      <c r="G1" s="69" t="inlineStr">
+      <c r="G1" s="107" t="inlineStr">
         <is>
           <t>Store Number</t>
         </is>
       </c>
-      <c r="H1" s="69" t="inlineStr">
+      <c r="H1" s="107" t="inlineStr">
         <is>
           <t>Common Name</t>
         </is>
       </c>
-      <c r="I1" s="69" t="inlineStr">
+      <c r="I1" s="107" t="inlineStr">
         <is>
           <t>Sub-Category</t>
         </is>
       </c>
-      <c r="J1" s="69" t="inlineStr">
+      <c r="J1" s="107" t="inlineStr">
         <is>
           <t>Date 1</t>
         </is>
       </c>
-      <c r="K1" s="69" t="inlineStr">
+      <c r="K1" s="107" t="inlineStr">
         <is>
           <t>Price 1</t>
         </is>
       </c>
-      <c r="L1" s="69" t="inlineStr">
+      <c r="L1" s="107" t="inlineStr">
         <is>
           <t>Date 2</t>
         </is>
       </c>
-      <c r="M1" s="69" t="inlineStr">
+      <c r="M1" s="107" t="inlineStr">
         <is>
           <t>Price 2</t>
         </is>
       </c>
-      <c r="N1" s="69" t="inlineStr">
+      <c r="N1" s="107" t="inlineStr">
         <is>
           <t>Date 3</t>
         </is>
       </c>
-      <c r="O1" s="69" t="inlineStr">
+      <c r="O1" s="107" t="inlineStr">
         <is>
           <t>Price 3</t>
         </is>
       </c>
-      <c r="P1" s="69" t="inlineStr">
+      <c r="P1" s="107" t="inlineStr">
         <is>
           <t>Date 4</t>
         </is>
       </c>
-      <c r="Q1" s="69" t="inlineStr">
+      <c r="Q1" s="107" t="inlineStr">
         <is>
           <t>Price 4</t>
         </is>
       </c>
-      <c r="R1" s="69" t="inlineStr">
+      <c r="R1" s="107" t="inlineStr">
         <is>
           <t>Date 5</t>
         </is>
       </c>
-      <c r="S1" s="69" t="inlineStr">
+      <c r="S1" s="107" t="inlineStr">
         <is>
           <t>Price 5</t>
         </is>
@@ -18596,8 +18609,988 @@
         <v>1.55</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="1">
+        <f>SUM(K148,M148,O148,Q148,S148)</f>
+        <v/>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>701574</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Frmhse Rnch Chd</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1">
+        <f>SUM(K149,M149,O149,Q149,S149)</f>
+        <v/>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>356457</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Organic Kale</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <f>SUM(K150,M150,O150,Q150,S150)</f>
+        <v/>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>356591</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pink Lady Apple</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Pink Lady Apple</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <f>SUM(K151,M151,O151,Q151,S151)</f>
+        <v/>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>356686</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Little Yellows</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <f>SUM(K152,M152,O152,Q152,S152)</f>
+        <v/>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>356427</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Multi-Peppers 3</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Multi-Peppers 3</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <f>SUM(K153,M153,O153,Q153,S153)</f>
+        <v/>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>396384</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Green Grapes LRW</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <f>SUM(K154,M154,O154,Q154,S154)</f>
+        <v/>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>356417</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Mandarins</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <f>SUM(K155,M155,O155,Q155,S155)</f>
+        <v/>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>692109</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Org Celery Heart</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <f>SUM(K156,M156,O156,Q156,S156)</f>
+        <v/>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>466249</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Head &amp; Shoulders</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <f>SUM(K157,M157,O157,Q157,S157)</f>
+        <v/>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>399518</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Salt Grinders</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1">
+        <f>SUM(K158,M158,O158,Q158,S158)</f>
+        <v/>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>399025</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Peppercorn Grinder</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Peppercorn Grind</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1">
+        <f>SUM(K159,M159,O159,Q159,S159)</f>
+        <v/>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Brocoli Crowns</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1">
+        <f>SUM(K160,M160,O160,Q160,S160)</f>
+        <v/>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Banannas LRW</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1">
+        <f>SUM(K161,M161,O161,Q161,S161)</f>
+        <v/>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Blueberries</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1">
+        <f>SUM(K162,M162,O162,Q162,S162)</f>
+        <v/>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Raspberries</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1">
+        <f>SUM(K163,M163,O163,Q163,S163)</f>
+        <v/>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Strawberries</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1">
+        <f>SUM(K164,M164,O164,Q164,S164)</f>
+        <v/>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>GF Wide Pan Bread</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1">
+        <f>SUM(K165,M165,O165,Q165,S165)</f>
+        <v/>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Artisinal Buns</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1">
+        <f>SUM(K166,M166,O166,Q166,S166)</f>
+        <v/>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Organic Chickpeas</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1">
+        <f>SUM(K167,M167,O167,Q167,S167)</f>
+        <v/>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Pil Flaky Biscuits</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S146"/>
+  <autoFilter ref="A1:S167"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31041,31 +32034,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="84" min="1" max="1"/>
     <col width="16" customWidth="1" style="84" min="2" max="3"/>
+    <col width="16" customWidth="1" style="84" min="3" max="3"/>
     <col width="22" customWidth="1" style="84" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="107" t="inlineStr">
         <is>
           <t>Source OCR JSON</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="107" t="inlineStr">
         <is>
           <t>Store Number</t>
         </is>
       </c>
-      <c r="C1" s="69" t="inlineStr">
+      <c r="C1" s="107" t="inlineStr">
         <is>
           <t>Receipt Date</t>
         </is>
       </c>
-      <c r="D1" s="69" t="inlineStr">
+      <c r="D1" s="107" t="inlineStr">
         <is>
           <t>Imported Timestamp</t>
         </is>
@@ -31303,6 +32297,42 @@
       </c>
       <c r="D14" s="3" t="n">
         <v>46268.78732697917</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>090626_ALDI_238_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="D15" s="134" t="n">
+        <v>46271.6522190625</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>090626_ALDI_238_B_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="D16" s="134" t="n">
+        <v>46271.65845203114</v>
       </c>
     </row>
   </sheetData>

--- a/data/database/shopgraph_purchase_history copy.xlsx
+++ b/data/database/shopgraph_purchase_history copy.xlsx
@@ -15,10 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imported Receipts" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP 9_26w1 26" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP 9_26w2 26" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$S$167</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Category Manager'!$A$1:$P$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purchase History'!$A$1:$U$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Category Manager'!$A$1:$S$69</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,15 +27,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm"/>
     <numFmt numFmtId="166" formatCode="mmm\ yyyy"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="mm/dd/yyyy hh:mm"/>
-    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -136,13 +135,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
-      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -155,13 +161,6 @@
       <family val="2"/>
       <b val="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -671,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -742,65 +741,65 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -861,8 +860,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="59" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -969,8 +968,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1060,6 +1057,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Monthly Spending</a:t>
             </a:r>
           </a:p>
@@ -1159,6 +1157,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Month Number</a:t>
                 </a:r>
               </a:p>
@@ -1195,6 +1194,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Spending ($)</a:t>
                 </a:r>
               </a:p>
@@ -4320,6 +4320,900 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Budget vs Category Spending</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AH1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="5B9BD5"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AH$2:$AH$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AI1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AI$2:$AI$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AJ1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AJ$2:$AJ$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AK1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="A5A5A5"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AK$2:$AK$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AL1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AL$2:$AL$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AM1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AM$2:$AM$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AN1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="255E91"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="255E91"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AN$2:$AN$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AO1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="9E480E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9E480E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AO$2:$AO$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AP1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="636363"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="636363"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AP$2:$AP$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AQ1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="997300"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="997300"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AQ$2:$AQ$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AR1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="264478"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="264478"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AR$2:$AR$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AS1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="43682B"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="43682B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AS$2:$AS$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AT1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8064A2"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AT$2:$AT$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AU1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4BACC6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AU$2:$AU$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AV1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="F79646"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AV$2:$AV$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="15"/>
+          <order val="15"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AW1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="92A9CF"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="92A9CF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AW$2:$AW$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="16"/>
+          <order val="16"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AX1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="95B3D7"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="95B3D7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AX$2:$AX$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="17"/>
+          <order val="17"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AY1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C0504D"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AY$2:$AY$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="18"/>
+          <order val="18"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!AZ1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="9BBB59"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AZ$2:$AZ$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!BA1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="7F7F7F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$BA$2:$BA$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="20"/>
+          <order val="20"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!BB1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="806000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="806000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$BB$2:$BB$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="21"/>
+          <order val="21"/>
+          <tx>
+            <strRef>
+              <f>'BP 9_26w2 26'!BC1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="ctr"/>
+              <showSerName val="1"/>
+            </dLbl>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'BP 9_26w2 26'!$AG$2:$AG$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'BP 9_26w2 26'!$BC$2:$BC$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="70"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Amount ($)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -4333,6 +5227,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Spending by Sub-Category</a:t>
             </a:r>
           </a:p>
@@ -5838,6 +6733,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Spending ($)</a:t>
                 </a:r>
               </a:p>
@@ -5874,6 +6770,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>Number</a:t>
                 </a:r>
               </a:p>
@@ -11103,6 +12000,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -11392,126 +12316,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S167"/>
+  <dimension ref="A1:U183"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="84" min="1" max="1"/>
     <col width="3" customWidth="1" style="84" min="2" max="2"/>
     <col width="18" customWidth="1" style="84" min="3" max="4"/>
-    <col width="18" customWidth="1" style="84" min="4" max="4"/>
     <col width="34" customWidth="1" style="84" min="5" max="5"/>
     <col width="14" customWidth="1" style="84" min="6" max="6"/>
     <col width="16" customWidth="1" style="84" min="7" max="7"/>
     <col width="28" bestFit="1" customWidth="1" style="84" min="8" max="8"/>
     <col width="22" customWidth="1" style="84" min="9" max="9"/>
-    <col width="14" customWidth="1" style="84" min="10" max="19"/>
-    <col width="14" customWidth="1" style="84" min="11" max="11"/>
-    <col width="14" customWidth="1" style="84" min="12" max="12"/>
-    <col width="14" customWidth="1" style="84" min="13" max="13"/>
-    <col width="14" customWidth="1" style="84" min="14" max="14"/>
-    <col width="14" customWidth="1" style="84" min="15" max="15"/>
-    <col width="14" customWidth="1" style="84" min="16" max="16"/>
-    <col width="14" customWidth="1" style="84" min="17" max="17"/>
-    <col width="14" customWidth="1" style="84" min="18" max="18"/>
-    <col width="14" customWidth="1" style="84" min="19" max="19"/>
+    <col width="14" customWidth="1" style="84" min="10" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="107" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B1" s="107" t="n"/>
-      <c r="C1" s="107" t="inlineStr">
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="69" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="D1" s="107" t="inlineStr">
+      <c r="D1" s="69" t="inlineStr">
         <is>
           <t>Six-Digit SKU</t>
         </is>
       </c>
-      <c r="E1" s="107" t="inlineStr">
+      <c r="E1" s="69" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="F1" s="107" t="inlineStr">
+      <c r="F1" s="69" t="inlineStr">
         <is>
           <t>Tax Code</t>
         </is>
       </c>
-      <c r="G1" s="107" t="inlineStr">
+      <c r="G1" s="69" t="inlineStr">
         <is>
           <t>Store Number</t>
         </is>
       </c>
-      <c r="H1" s="107" t="inlineStr">
+      <c r="H1" s="69" t="inlineStr">
         <is>
           <t>Common Name</t>
         </is>
       </c>
-      <c r="I1" s="107" t="inlineStr">
+      <c r="I1" s="69" t="inlineStr">
         <is>
           <t>Sub-Category</t>
         </is>
       </c>
-      <c r="J1" s="107" t="inlineStr">
+      <c r="J1" s="69" t="inlineStr">
         <is>
           <t>Date 1</t>
         </is>
       </c>
-      <c r="K1" s="107" t="inlineStr">
+      <c r="K1" s="69" t="inlineStr">
         <is>
           <t>Price 1</t>
         </is>
       </c>
-      <c r="L1" s="107" t="inlineStr">
+      <c r="L1" s="69" t="inlineStr">
         <is>
           <t>Date 2</t>
         </is>
       </c>
-      <c r="M1" s="107" t="inlineStr">
+      <c r="M1" s="69" t="inlineStr">
         <is>
           <t>Price 2</t>
         </is>
       </c>
-      <c r="N1" s="107" t="inlineStr">
+      <c r="N1" s="69" t="inlineStr">
         <is>
           <t>Date 3</t>
         </is>
       </c>
-      <c r="O1" s="107" t="inlineStr">
+      <c r="O1" s="69" t="inlineStr">
         <is>
           <t>Price 3</t>
         </is>
       </c>
-      <c r="P1" s="107" t="inlineStr">
+      <c r="P1" s="69" t="inlineStr">
         <is>
           <t>Date 4</t>
         </is>
       </c>
-      <c r="Q1" s="107" t="inlineStr">
+      <c r="Q1" s="69" t="inlineStr">
         <is>
           <t>Price 4</t>
         </is>
       </c>
-      <c r="R1" s="107" t="inlineStr">
+      <c r="R1" s="69" t="inlineStr">
         <is>
           <t>Date 5</t>
         </is>
       </c>
-      <c r="S1" s="107" t="inlineStr">
+      <c r="S1" s="69" t="inlineStr">
         <is>
           <t>Price 5</t>
+        </is>
+      </c>
+      <c r="T1" s="69" t="inlineStr">
+        <is>
+          <t>Date 6</t>
+        </is>
+      </c>
+      <c r="U1" s="69" t="inlineStr">
+        <is>
+          <t>Price 6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <f>SUM(K2,M2,O2,Q2,S2)</f>
+        <f>SUM(K2,M2,O2,Q2,S2,U2)</f>
         <v/>
       </c>
       <c r="C2" t="inlineStr">
@@ -11558,7 +12482,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <f>SUM(K3,M3,O3,Q3,S3)</f>
+        <f>SUM(K3,M3,O3,Q3,S3,U3)</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -11605,7 +12529,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <f>SUM(K4,M4,O4,Q4,S4)</f>
+        <f>SUM(K4,M4,O4,Q4,S4,U4)</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
@@ -11652,7 +12576,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <f>SUM(K5,M5,O5,Q5,S5)</f>
+        <f>SUM(K5,M5,O5,Q5,S5,U5)</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -11705,7 +12629,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <f>SUM(K6,M6,O6,Q6,S6)</f>
+        <f>SUM(K6,M6,O6,Q6,S6,U6)</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -11752,7 +12676,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <f>SUM(K7,M7,O7,Q7,S7)</f>
+        <f>SUM(K7,M7,O7,Q7,S7,U7)</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
@@ -11811,7 +12735,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <f>SUM(K8,M8,O8,Q8,S8)</f>
+        <f>SUM(K8,M8,O8,Q8,S8,U8)</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">
@@ -11858,7 +12782,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <f>SUM(K9,M9,O9,Q9,S9)</f>
+        <f>SUM(K9,M9,O9,Q9,S9,U9)</f>
         <v/>
       </c>
       <c r="C9" t="inlineStr">
@@ -11905,7 +12829,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <f>SUM(K10,M10,O10,Q10,S10)</f>
+        <f>SUM(K10,M10,O10,Q10,S10,U10)</f>
         <v/>
       </c>
       <c r="C10" t="inlineStr">
@@ -11952,7 +12876,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <f>SUM(K11,M11,O11,Q11,S11)</f>
+        <f>SUM(K11,M11,O11,Q11,S11,U11)</f>
         <v/>
       </c>
       <c r="C11" t="inlineStr">
@@ -11999,7 +12923,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <f>SUM(K12,M12,O12,Q12,S12)</f>
+        <f>SUM(K12,M12,O12,Q12,S12,U12)</f>
         <v/>
       </c>
       <c r="C12" t="inlineStr">
@@ -12046,7 +12970,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <f>SUM(K13,M13,O13,Q13,S13)</f>
+        <f>SUM(K13,M13,O13,Q13,S13,U13)</f>
         <v/>
       </c>
       <c r="C13" t="inlineStr">
@@ -12093,7 +13017,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <f>SUM(K14,M14,O14,Q14,S14)</f>
+        <f>SUM(K14,M14,O14,Q14,S14,U14)</f>
         <v/>
       </c>
       <c r="C14" t="inlineStr">
@@ -12140,7 +13064,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <f>SUM(K15,M15,O15,Q15,S15)</f>
+        <f>SUM(K15,M15,O15,Q15,S15,U15)</f>
         <v/>
       </c>
       <c r="C15" t="inlineStr">
@@ -12187,7 +13111,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <f>SUM(K16,M16,O16,Q16,S16)</f>
+        <f>SUM(K16,M16,O16,Q16,S16,U16)</f>
         <v/>
       </c>
       <c r="C16" t="inlineStr">
@@ -12234,7 +13158,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <f>SUM(K17,M17,O17,Q17,S17)</f>
+        <f>SUM(K17,M17,O17,Q17,S17,U17)</f>
         <v/>
       </c>
       <c r="C17" t="inlineStr">
@@ -12281,7 +13205,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <f>SUM(K18,M18,O18,Q18,S18)</f>
+        <f>SUM(K18,M18,O18,Q18,S18,U18)</f>
         <v/>
       </c>
       <c r="C18" t="inlineStr">
@@ -12328,7 +13252,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <f>SUM(K19,M19,O19,Q19,S19)</f>
+        <f>SUM(K19,M19,O19,Q19,S19,U19)</f>
         <v/>
       </c>
       <c r="C19" t="inlineStr">
@@ -12375,7 +13299,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <f>SUM(K20,M20,O20,Q20,S20)</f>
+        <f>SUM(K20,M20,O20,Q20,S20,U20)</f>
         <v/>
       </c>
       <c r="C20" t="inlineStr">
@@ -12422,7 +13346,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <f>SUM(K21,M21,O21,Q21,S21)</f>
+        <f>SUM(K21,M21,O21,Q21,S21,U21)</f>
         <v/>
       </c>
       <c r="C21" t="inlineStr">
@@ -12469,7 +13393,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <f>SUM(K22,M22,O22,Q22,S22)</f>
+        <f>SUM(K22,M22,O22,Q22,S22,U22)</f>
         <v/>
       </c>
       <c r="C22" t="inlineStr">
@@ -12516,7 +13440,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <f>SUM(K23,M23,O23,Q23,S23)</f>
+        <f>SUM(K23,M23,O23,Q23,S23,U23)</f>
         <v/>
       </c>
       <c r="C23" t="inlineStr">
@@ -12563,7 +13487,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <f>SUM(K24,M24,O24,Q24,S24)</f>
+        <f>SUM(K24,M24,O24,Q24,S24,U24)</f>
         <v/>
       </c>
       <c r="C24" t="inlineStr">
@@ -12610,7 +13534,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <f>SUM(K25,M25,O25,Q25,S25)</f>
+        <f>SUM(K25,M25,O25,Q25,S25,U25)</f>
         <v/>
       </c>
       <c r="C25" t="inlineStr">
@@ -12657,7 +13581,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <f>SUM(K26,M26,O26,Q26,S26)</f>
+        <f>SUM(K26,M26,O26,Q26,S26,U26)</f>
         <v/>
       </c>
       <c r="C26" t="inlineStr">
@@ -12710,7 +13634,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <f>SUM(K27,M27,O27,Q27,S27)</f>
+        <f>SUM(K27,M27,O27,Q27,S27,U27)</f>
         <v/>
       </c>
       <c r="C27" t="inlineStr">
@@ -12757,7 +13681,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <f>SUM(K28,M28,O28,Q28,S28)</f>
+        <f>SUM(K28,M28,O28,Q28,S28,U28)</f>
         <v/>
       </c>
       <c r="C28" t="inlineStr">
@@ -12810,7 +13734,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1">
-        <f>SUM(K29,M29,O29,Q29,S29)</f>
+        <f>SUM(K29,M29,O29,Q29,S29,U29)</f>
         <v/>
       </c>
       <c r="C29" t="inlineStr">
@@ -12863,7 +13787,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <f>SUM(K30,M30,O30,Q30,S30)</f>
+        <f>SUM(K30,M30,O30,Q30,S30,U30)</f>
         <v/>
       </c>
       <c r="C30" t="inlineStr">
@@ -12910,7 +13834,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <f>SUM(K31,M31,O31,Q31,S31)</f>
+        <f>SUM(K31,M31,O31,Q31,S31,U31)</f>
         <v/>
       </c>
       <c r="C31" t="inlineStr">
@@ -12957,7 +13881,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1">
-        <f>SUM(K32,M32,O32,Q32,S32)</f>
+        <f>SUM(K32,M32,O32,Q32,S32,U32)</f>
         <v/>
       </c>
       <c r="C32" t="inlineStr">
@@ -13004,7 +13928,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <f>SUM(K33,M33,O33,Q33,S33)</f>
+        <f>SUM(K33,M33,O33,Q33,S33,U33)</f>
         <v/>
       </c>
       <c r="C33" t="inlineStr">
@@ -13051,7 +13975,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1">
-        <f>SUM(K34,M34,O34,Q34,S34)</f>
+        <f>SUM(K34,M34,O34,Q34,S34,U34)</f>
         <v/>
       </c>
       <c r="C34" t="inlineStr">
@@ -13098,7 +14022,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <f>SUM(K35,M35,O35,Q35,S35)</f>
+        <f>SUM(K35,M35,O35,Q35,S35,U35)</f>
         <v/>
       </c>
       <c r="C35" t="inlineStr">
@@ -13145,7 +14069,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1">
-        <f>SUM(K36,M36,O36,Q36,S36)</f>
+        <f>SUM(K36,M36,O36,Q36,S36,U36)</f>
         <v/>
       </c>
       <c r="C36" t="inlineStr">
@@ -13192,7 +14116,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1">
-        <f>SUM(K37,M37,O37,Q37,S37)</f>
+        <f>SUM(K37,M37,O37,Q37,S37,U37)</f>
         <v/>
       </c>
       <c r="C37" t="inlineStr">
@@ -13239,7 +14163,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1">
-        <f>SUM(K38,M38,O38,Q38,S38)</f>
+        <f>SUM(K38,M38,O38,Q38,S38,U38)</f>
         <v/>
       </c>
       <c r="C38" t="inlineStr">
@@ -13286,7 +14210,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1">
-        <f>SUM(K39,M39,O39,Q39,S39)</f>
+        <f>SUM(K39,M39,O39,Q39,S39,U39)</f>
         <v/>
       </c>
       <c r="C39" t="inlineStr">
@@ -13333,7 +14257,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1">
-        <f>SUM(K40,M40,O40,Q40,S40)</f>
+        <f>SUM(K40,M40,O40,Q40,S40,U40)</f>
         <v/>
       </c>
       <c r="C40" t="inlineStr">
@@ -13383,10 +14307,34 @@
       <c r="M40" s="1" t="n">
         <v>6.99</v>
       </c>
+      <c r="N40" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O40" s="1" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="U40" t="n">
+        <v>6.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <f>SUM(K41,M41,O41,Q41,S41)</f>
+        <f>SUM(K41,M41,O41,Q41,S41,U41)</f>
         <v/>
       </c>
       <c r="C41" t="inlineStr">
@@ -13433,7 +14381,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <f>SUM(K42,M42,O42,Q42,S42)</f>
+        <f>SUM(K42,M42,O42,Q42,S42,U42)</f>
         <v/>
       </c>
       <c r="C42" t="inlineStr">
@@ -13480,7 +14428,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <f>SUM(K43,M43,O43,Q43,S43)</f>
+        <f>SUM(K43,M43,O43,Q43,S43,U43)</f>
         <v/>
       </c>
       <c r="C43" t="inlineStr">
@@ -13527,7 +14475,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <f>SUM(K44,M44,O44,Q44,S44)</f>
+        <f>SUM(K44,M44,O44,Q44,S44,U44)</f>
         <v/>
       </c>
       <c r="C44" t="inlineStr">
@@ -13571,10 +14519,26 @@
       <c r="K44" s="1" t="n">
         <v>5.99</v>
       </c>
+      <c r="L44" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <f>SUM(K45,M45,O45,Q45,S45)</f>
+        <f>SUM(K45,M45,O45,Q45,S45,U45)</f>
         <v/>
       </c>
       <c r="C45" t="inlineStr">
@@ -13621,7 +14585,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <f>SUM(K46,M46,O46,Q46,S46)</f>
+        <f>SUM(K46,M46,O46,Q46,S46,U46)</f>
         <v/>
       </c>
       <c r="C46" t="inlineStr">
@@ -13668,7 +14632,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <f>SUM(K47,M47,O47,Q47,S47)</f>
+        <f>SUM(K47,M47,O47,Q47,S47,U47)</f>
         <v/>
       </c>
       <c r="C47" t="inlineStr">
@@ -13715,7 +14679,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <f>SUM(K48,M48,O48,Q48,S48)</f>
+        <f>SUM(K48,M48,O48,Q48,S48,U48)</f>
         <v/>
       </c>
       <c r="C48" t="inlineStr">
@@ -13762,7 +14726,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1">
-        <f>SUM(K49,M49,O49,Q49,S49)</f>
+        <f>SUM(K49,M49,O49,Q49,S49,U49)</f>
         <v/>
       </c>
       <c r="C49" t="inlineStr">
@@ -13809,7 +14773,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1">
-        <f>SUM(K50,M50,O50,Q50,S50)</f>
+        <f>SUM(K50,M50,O50,Q50,S50,U50)</f>
         <v/>
       </c>
       <c r="C50" t="inlineStr">
@@ -13856,7 +14820,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <f>SUM(K51,M51,O51,Q51,S51)</f>
+        <f>SUM(K51,M51,O51,Q51,S51,U51)</f>
         <v/>
       </c>
       <c r="C51" t="inlineStr">
@@ -13909,7 +14873,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <f>SUM(K52,M52,O52,Q52,S52)</f>
+        <f>SUM(K52,M52,O52,Q52,S52,U52)</f>
         <v/>
       </c>
       <c r="C52" t="inlineStr">
@@ -13962,7 +14926,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1">
-        <f>SUM(K53,M53,O53,Q53,S53)</f>
+        <f>SUM(K53,M53,O53,Q53,S53,U53)</f>
         <v/>
       </c>
       <c r="C53" t="inlineStr">
@@ -14015,7 +14979,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <f>SUM(K54,M54,O54,Q54,S54)</f>
+        <f>SUM(K54,M54,O54,Q54,S54,U54)</f>
         <v/>
       </c>
       <c r="C54" t="inlineStr">
@@ -14062,7 +15026,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <f>SUM(K55,M55,O55,Q55,S55)</f>
+        <f>SUM(K55,M55,O55,Q55,S55,U55)</f>
         <v/>
       </c>
       <c r="C55" t="inlineStr">
@@ -14115,7 +15079,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <f>SUM(K56,M56,O56,Q56,S56)</f>
+        <f>SUM(K56,M56,O56,Q56,S56,U56)</f>
         <v/>
       </c>
       <c r="C56" t="inlineStr">
@@ -14168,7 +15132,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1">
-        <f>SUM(K57,M57,O57,Q57,S57)</f>
+        <f>SUM(K57,M57,O57,Q57,S57,U57)</f>
         <v/>
       </c>
       <c r="C57" t="inlineStr">
@@ -14221,7 +15185,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1">
-        <f>SUM(K58,M58,O58,Q58,S58)</f>
+        <f>SUM(K58,M58,O58,Q58,S58,U58)</f>
         <v/>
       </c>
       <c r="C58" t="inlineStr">
@@ -14268,7 +15232,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1">
-        <f>SUM(K59,M59,O59,Q59,S59)</f>
+        <f>SUM(K59,M59,O59,Q59,S59,U59)</f>
         <v/>
       </c>
       <c r="C59" t="inlineStr">
@@ -14315,7 +15279,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1">
-        <f>SUM(K60,M60,O60,Q60,S60)</f>
+        <f>SUM(K60,M60,O60,Q60,S60,U60)</f>
         <v/>
       </c>
       <c r="C60" t="inlineStr">
@@ -14368,7 +15332,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1">
-        <f>SUM(K61,M61,O61,Q61,S61)</f>
+        <f>SUM(K61,M61,O61,Q61,S61,U61)</f>
         <v/>
       </c>
       <c r="C61" t="inlineStr">
@@ -14421,7 +15385,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1">
-        <f>SUM(K62,M62,O62,Q62,S62)</f>
+        <f>SUM(K62,M62,O62,Q62,S62,U62)</f>
         <v/>
       </c>
       <c r="C62" t="inlineStr">
@@ -14468,7 +15432,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1">
-        <f>SUM(K63,M63,O63,Q63,S63)</f>
+        <f>SUM(K63,M63,O63,Q63,S63,U63)</f>
         <v/>
       </c>
       <c r="C63" t="inlineStr">
@@ -14521,7 +15485,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1">
-        <f>SUM(K64,M64,O64,Q64,S64)</f>
+        <f>SUM(K64,M64,O64,Q64,S64,U64)</f>
         <v/>
       </c>
       <c r="C64" t="inlineStr">
@@ -14574,7 +15538,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1">
-        <f>SUM(K65,M65,O65,Q65,S65)</f>
+        <f>SUM(K65,M65,O65,Q65,S65,U65)</f>
         <v/>
       </c>
       <c r="C65" t="inlineStr">
@@ -14627,7 +15591,7 @@
     </row>
     <row r="66">
       <c r="A66" s="1">
-        <f>SUM(K66,M66,O66,Q66,S66)</f>
+        <f>SUM(K66,M66,O66,Q66,S66,U66)</f>
         <v/>
       </c>
       <c r="C66" t="inlineStr">
@@ -14680,7 +15644,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1">
-        <f>SUM(K67,M67,O67,Q67,S67)</f>
+        <f>SUM(K67,M67,O67,Q67,S67,U67)</f>
         <v/>
       </c>
       <c r="C67" t="inlineStr">
@@ -14727,7 +15691,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1">
-        <f>SUM(K68,M68,O68,Q68,S68)</f>
+        <f>SUM(K68,M68,O68,Q68,S68,U68)</f>
         <v/>
       </c>
       <c r="C68" t="inlineStr">
@@ -14780,7 +15744,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1">
-        <f>SUM(K69,M69,O69,Q69,S69)</f>
+        <f>SUM(K69,M69,O69,Q69,S69,U69)</f>
         <v/>
       </c>
       <c r="C69" t="inlineStr">
@@ -14833,7 +15797,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1">
-        <f>SUM(K70,M70,O70,Q70,S70)</f>
+        <f>SUM(K70,M70,O70,Q70,S70,U70)</f>
         <v/>
       </c>
       <c r="C70" t="inlineStr">
@@ -14892,7 +15856,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1">
-        <f>SUM(K71,M71,O71,Q71,S71)</f>
+        <f>SUM(K71,M71,O71,Q71,S71,U71)</f>
         <v/>
       </c>
       <c r="C71" t="inlineStr">
@@ -14945,7 +15909,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1">
-        <f>SUM(K72,M72,O72,Q72,S72)</f>
+        <f>SUM(K72,M72,O72,Q72,S72,U72)</f>
         <v/>
       </c>
       <c r="C72" t="inlineStr">
@@ -14992,7 +15956,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1">
-        <f>SUM(K73,M73,O73,Q73,S73)</f>
+        <f>SUM(K73,M73,O73,Q73,S73,U73)</f>
         <v/>
       </c>
       <c r="C73" t="inlineStr">
@@ -15063,7 +16027,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1">
-        <f>SUM(K74,M74,O74,Q74,S74)</f>
+        <f>SUM(K74,M74,O74,Q74,S74,U74)</f>
         <v/>
       </c>
       <c r="C74" t="inlineStr">
@@ -15122,7 +16086,7 @@
     </row>
     <row r="75">
       <c r="A75" s="1">
-        <f>SUM(K75,M75,O75,Q75,S75)</f>
+        <f>SUM(K75,M75,O75,Q75,S75,U75)</f>
         <v/>
       </c>
       <c r="C75" t="inlineStr">
@@ -15169,7 +16133,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1">
-        <f>SUM(K76,M76,O76,Q76,S76)</f>
+        <f>SUM(K76,M76,O76,Q76,S76,U76)</f>
         <v/>
       </c>
       <c r="C76" t="inlineStr">
@@ -15216,7 +16180,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1">
-        <f>SUM(K77,M77,O77,Q77,S77)</f>
+        <f>SUM(K77,M77,O77,Q77,S77,U77)</f>
         <v/>
       </c>
       <c r="C77" t="inlineStr">
@@ -15263,7 +16227,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1">
-        <f>SUM(K78,M78,O78,Q78,S78)</f>
+        <f>SUM(K78,M78,O78,Q78,S78,U78)</f>
         <v/>
       </c>
       <c r="C78" t="inlineStr">
@@ -15310,7 +16274,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1">
-        <f>SUM(K79,M79,O79,Q79,S79)</f>
+        <f>SUM(K79,M79,O79,Q79,S79,U79)</f>
         <v/>
       </c>
       <c r="C79" t="inlineStr">
@@ -15357,7 +16321,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1">
-        <f>SUM(K80,M80,O80,Q80,S80)</f>
+        <f>SUM(K80,M80,O80,Q80,S80,U80)</f>
         <v/>
       </c>
       <c r="C80" t="inlineStr">
@@ -15404,7 +16368,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1">
-        <f>SUM(K81,M81,O81,Q81,S81)</f>
+        <f>SUM(K81,M81,O81,Q81,S81,U81)</f>
         <v/>
       </c>
       <c r="C81" t="inlineStr">
@@ -15451,7 +16415,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1">
-        <f>SUM(K82,M82,O82,Q82,S82)</f>
+        <f>SUM(K82,M82,O82,Q82,S82,U82)</f>
         <v/>
       </c>
       <c r="C82" t="inlineStr">
@@ -15498,7 +16462,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1">
-        <f>SUM(K83,M83,O83,Q83,S83)</f>
+        <f>SUM(K83,M83,O83,Q83,S83,U83)</f>
         <v/>
       </c>
       <c r="C83" t="inlineStr">
@@ -15545,7 +16509,7 @@
     </row>
     <row r="84">
       <c r="A84" s="1">
-        <f>SUM(K84,M84,O84,Q84,S84)</f>
+        <f>SUM(K84,M84,O84,Q84,S84,U84)</f>
         <v/>
       </c>
       <c r="C84" t="inlineStr">
@@ -15592,7 +16556,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1">
-        <f>SUM(K85,M85,O85,Q85,S85)</f>
+        <f>SUM(K85,M85,O85,Q85,S85,U85)</f>
         <v/>
       </c>
       <c r="C85" t="inlineStr">
@@ -15639,7 +16603,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1">
-        <f>SUM(K86,M86,O86,Q86,S86)</f>
+        <f>SUM(K86,M86,O86,Q86,S86,U86)</f>
         <v/>
       </c>
       <c r="C86" t="inlineStr">
@@ -15686,7 +16650,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1">
-        <f>SUM(K87,M87,O87,Q87,S87)</f>
+        <f>SUM(K87,M87,O87,Q87,S87,U87)</f>
         <v/>
       </c>
       <c r="C87" t="inlineStr">
@@ -15733,7 +16697,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1">
-        <f>SUM(K88,M88,O88,Q88,S88)</f>
+        <f>SUM(K88,M88,O88,Q88,S88,U88)</f>
         <v/>
       </c>
       <c r="C88" t="inlineStr">
@@ -15780,7 +16744,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1">
-        <f>SUM(K89,M89,O89,Q89,S89)</f>
+        <f>SUM(K89,M89,O89,Q89,S89,U89)</f>
         <v/>
       </c>
       <c r="C89" t="inlineStr">
@@ -15827,7 +16791,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1">
-        <f>SUM(K90,M90,O90,Q90,S90)</f>
+        <f>SUM(K90,M90,O90,Q90,S90,U90)</f>
         <v/>
       </c>
       <c r="C90" t="inlineStr">
@@ -15874,7 +16838,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1">
-        <f>SUM(K91,M91,O91,Q91,S91)</f>
+        <f>SUM(K91,M91,O91,Q91,S91,U91)</f>
         <v/>
       </c>
       <c r="C91" t="inlineStr">
@@ -15921,7 +16885,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1">
-        <f>SUM(K92,M92,O92,Q92,S92)</f>
+        <f>SUM(K92,M92,O92,Q92,S92,U92)</f>
         <v/>
       </c>
       <c r="C92" t="inlineStr">
@@ -15968,7 +16932,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1">
-        <f>SUM(K93,M93,O93,Q93,S93)</f>
+        <f>SUM(K93,M93,O93,Q93,S93,U93)</f>
         <v/>
       </c>
       <c r="C93" t="inlineStr">
@@ -16015,7 +16979,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1">
-        <f>SUM(K94,M94,O94,Q94,S94)</f>
+        <f>SUM(K94,M94,O94,Q94,S94,U94)</f>
         <v/>
       </c>
       <c r="C94" t="inlineStr">
@@ -16062,7 +17026,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1">
-        <f>SUM(K95,M95,O95,Q95,S95)</f>
+        <f>SUM(K95,M95,O95,Q95,S95,U95)</f>
         <v/>
       </c>
       <c r="C95" t="inlineStr">
@@ -16115,7 +17079,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1">
-        <f>SUM(K96,M96,O96,Q96,S96)</f>
+        <f>SUM(K96,M96,O96,Q96,S96,U96)</f>
         <v/>
       </c>
       <c r="C96" t="inlineStr">
@@ -16168,7 +17132,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1">
-        <f>SUM(K97,M97,O97,Q97,S97)</f>
+        <f>SUM(K97,M97,O97,Q97,S97,U97)</f>
         <v/>
       </c>
       <c r="C97" t="inlineStr">
@@ -16221,7 +17185,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1">
-        <f>SUM(K98,M98,O98,Q98,S98)</f>
+        <f>SUM(K98,M98,O98,Q98,S98,U98)</f>
         <v/>
       </c>
       <c r="C98" t="inlineStr">
@@ -16268,7 +17232,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1">
-        <f>SUM(K99,M99,O99,Q99,S99)</f>
+        <f>SUM(K99,M99,O99,Q99,S99,U99)</f>
         <v/>
       </c>
       <c r="C99" t="inlineStr">
@@ -16321,7 +17285,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1">
-        <f>SUM(K100,M100,O100,Q100,S100)</f>
+        <f>SUM(K100,M100,O100,Q100,S100,U100)</f>
         <v/>
       </c>
       <c r="C100" t="inlineStr">
@@ -16368,7 +17332,7 @@
     </row>
     <row r="101">
       <c r="A101" s="1">
-        <f>SUM(K101,M101,O101,Q101,S101)</f>
+        <f>SUM(K101,M101,O101,Q101,S101,U101)</f>
         <v/>
       </c>
       <c r="C101" t="inlineStr">
@@ -16417,7 +17381,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1">
-        <f>SUM(K102,M102,O102,Q102,S102)</f>
+        <f>SUM(K102,M102,O102,Q102,S102,U102)</f>
         <v/>
       </c>
       <c r="C102" t="inlineStr">
@@ -16464,7 +17428,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1">
-        <f>SUM(K103,M103,O103,Q103,S103)</f>
+        <f>SUM(K103,M103,O103,Q103,S103,U103)</f>
         <v/>
       </c>
       <c r="C103" t="inlineStr">
@@ -16511,7 +17475,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1">
-        <f>SUM(K104,M104,O104,Q104,S104)</f>
+        <f>SUM(K104,M104,O104,Q104,S104,U104)</f>
         <v/>
       </c>
       <c r="C104" t="inlineStr">
@@ -16558,7 +17522,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1">
-        <f>SUM(K105,M105,O105,Q105,S105)</f>
+        <f>SUM(K105,M105,O105,Q105,S105,U105)</f>
         <v/>
       </c>
       <c r="C105" t="inlineStr">
@@ -16605,7 +17569,7 @@
     </row>
     <row r="106">
       <c r="A106" s="1">
-        <f>SUM(K106,M106,O106,Q106,S106)</f>
+        <f>SUM(K106,M106,O106,Q106,S106,U106)</f>
         <v/>
       </c>
       <c r="C106" t="inlineStr">
@@ -16658,7 +17622,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1">
-        <f>SUM(K107,M107,O107,Q107,S107)</f>
+        <f>SUM(K107,M107,O107,Q107,S107,U107)</f>
         <v/>
       </c>
       <c r="C107" t="inlineStr">
@@ -16705,7 +17669,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1">
-        <f>SUM(K108,M108,O108,Q108,S108)</f>
+        <f>SUM(K108,M108,O108,Q108,S108,U108)</f>
         <v/>
       </c>
       <c r="C108" t="inlineStr">
@@ -16752,7 +17716,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1">
-        <f>SUM(K109,M109,O109,Q109,S109)</f>
+        <f>SUM(K109,M109,O109,Q109,S109,U109)</f>
         <v/>
       </c>
       <c r="C109" t="inlineStr">
@@ -16799,7 +17763,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1">
-        <f>SUM(K110,M110,O110,Q110,S110)</f>
+        <f>SUM(K110,M110,O110,Q110,S110,U110)</f>
         <v/>
       </c>
       <c r="C110" t="inlineStr">
@@ -16846,7 +17810,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1">
-        <f>SUM(K111,M111,O111,Q111,S111)</f>
+        <f>SUM(K111,M111,O111,Q111,S111,U111)</f>
         <v/>
       </c>
       <c r="C111" t="inlineStr">
@@ -16893,7 +17857,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1">
-        <f>SUM(K112,M112,O112,Q112,S112)</f>
+        <f>SUM(K112,M112,O112,Q112,S112,U112)</f>
         <v/>
       </c>
       <c r="C112" t="inlineStr">
@@ -16940,7 +17904,7 @@
     </row>
     <row r="113">
       <c r="A113" s="1">
-        <f>SUM(K113,M113,O113,Q113,S113)</f>
+        <f>SUM(K113,M113,O113,Q113,S113,U113)</f>
         <v/>
       </c>
       <c r="C113" t="inlineStr">
@@ -16987,7 +17951,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1">
-        <f>SUM(K114,M114,O114,Q114,S114)</f>
+        <f>SUM(K114,M114,O114,Q114,S114,U114)</f>
         <v/>
       </c>
       <c r="C114" t="inlineStr">
@@ -17034,7 +17998,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1">
-        <f>SUM(K115,M115,O115,Q115,S115)</f>
+        <f>SUM(K115,M115,O115,Q115,S115,U115)</f>
         <v/>
       </c>
       <c r="C115" t="inlineStr">
@@ -17081,7 +18045,7 @@
     </row>
     <row r="116">
       <c r="A116" s="1">
-        <f>SUM(K116,M116,O116,Q116,S116)</f>
+        <f>SUM(K116,M116,O116,Q116,S116,U116)</f>
         <v/>
       </c>
       <c r="C116" t="inlineStr">
@@ -17128,7 +18092,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1">
-        <f>SUM(K117,M117,O117,Q117,S117)</f>
+        <f>SUM(K117,M117,O117,Q117,S117,U117)</f>
         <v/>
       </c>
       <c r="C117" t="inlineStr">
@@ -17175,7 +18139,7 @@
     </row>
     <row r="118">
       <c r="A118" s="1">
-        <f>SUM(K118,M118,O118,Q118,S118)</f>
+        <f>SUM(K118,M118,O118,Q118,S118,U118)</f>
         <v/>
       </c>
       <c r="C118" t="inlineStr">
@@ -17230,7 +18194,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1">
-        <f>SUM(K119,M119,O119,Q119,S119)</f>
+        <f>SUM(K119,M119,O119,Q119,S119,U119)</f>
         <v/>
       </c>
       <c r="C119" t="inlineStr">
@@ -17283,7 +18247,7 @@
     </row>
     <row r="120">
       <c r="A120" s="1">
-        <f>SUM(K120,M120,O120,Q120,S120)</f>
+        <f>SUM(K120,M120,O120,Q120,S120,U120)</f>
         <v/>
       </c>
       <c r="C120" t="inlineStr">
@@ -17330,7 +18294,7 @@
     </row>
     <row r="121">
       <c r="A121" s="1">
-        <f>SUM(K121,M121,O121,Q121,S121)</f>
+        <f>SUM(K121,M121,O121,Q121,S121,U121)</f>
         <v/>
       </c>
       <c r="C121" t="inlineStr">
@@ -17377,7 +18341,7 @@
     </row>
     <row r="122">
       <c r="A122" s="1">
-        <f>SUM(K122,M122,O122,Q122,S122)</f>
+        <f>SUM(K122,M122,O122,Q122,S122,U122)</f>
         <v/>
       </c>
       <c r="C122" t="inlineStr">
@@ -17424,7 +18388,7 @@
     </row>
     <row r="123">
       <c r="A123" s="1">
-        <f>SUM(K123,M123,O123,Q123,S123)</f>
+        <f>SUM(K123,M123,O123,Q123,S123,U123)</f>
         <v/>
       </c>
       <c r="C123" t="inlineStr">
@@ -17471,7 +18435,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1">
-        <f>SUM(K124,M124,O124,Q124,S124)</f>
+        <f>SUM(K124,M124,O124,Q124,S124,U124)</f>
         <v/>
       </c>
       <c r="C124" t="inlineStr">
@@ -17518,7 +18482,7 @@
     </row>
     <row r="125">
       <c r="A125" s="1">
-        <f>SUM(K125,M125,O125,Q125,S125)</f>
+        <f>SUM(K125,M125,O125,Q125,S125,U125)</f>
         <v/>
       </c>
       <c r="C125" t="inlineStr">
@@ -17565,7 +18529,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1">
-        <f>SUM(K126,M126,O126,Q126,S126)</f>
+        <f>SUM(K126,M126,O126,Q126,S126,U126)</f>
         <v/>
       </c>
       <c r="C126" t="inlineStr">
@@ -17612,7 +18576,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1">
-        <f>SUM(K127,M127,O127,Q127,S127)</f>
+        <f>SUM(K127,M127,O127,Q127,S127,U127)</f>
         <v/>
       </c>
       <c r="C127" t="inlineStr">
@@ -17665,7 +18629,7 @@
     </row>
     <row r="128">
       <c r="A128" s="1">
-        <f>SUM(K128,M128,O128,Q128,S128)</f>
+        <f>SUM(K128,M128,O128,Q128,S128,U128)</f>
         <v/>
       </c>
       <c r="C128" t="inlineStr">
@@ -17712,7 +18676,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1">
-        <f>SUM(K129,M129,O129,Q129,S129)</f>
+        <f>SUM(K129,M129,O129,Q129,S129,U129)</f>
         <v/>
       </c>
       <c r="C129" t="inlineStr">
@@ -17759,7 +18723,7 @@
     </row>
     <row r="130">
       <c r="A130" s="1">
-        <f>SUM(K130,M130,O130,Q130,S130)</f>
+        <f>SUM(K130,M130,O130,Q130,S130,U130)</f>
         <v/>
       </c>
       <c r="C130" t="inlineStr">
@@ -17806,7 +18770,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1">
-        <f>SUM(K131,M131,O131,Q131,S131)</f>
+        <f>SUM(K131,M131,O131,Q131,S131,U131)</f>
         <v/>
       </c>
       <c r="C131" t="inlineStr">
@@ -17853,7 +18817,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1">
-        <f>SUM(K132,M132,O132,Q132,S132)</f>
+        <f>SUM(K132,M132,O132,Q132,S132,U132)</f>
         <v/>
       </c>
       <c r="C132" t="inlineStr">
@@ -17900,7 +18864,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1">
-        <f>SUM(K133,M133,O133,Q133,S133)</f>
+        <f>SUM(K133,M133,O133,Q133,S133,U133)</f>
         <v/>
       </c>
       <c r="C133" t="inlineStr">
@@ -17947,7 +18911,7 @@
     </row>
     <row r="134">
       <c r="A134" s="1">
-        <f>SUM(K134,M134,O134,Q134,S134)</f>
+        <f>SUM(K134,M134,O134,Q134,S134,U134)</f>
         <v/>
       </c>
       <c r="C134" t="inlineStr">
@@ -17994,7 +18958,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1">
-        <f>SUM(K135,M135,O135,Q135,S135)</f>
+        <f>SUM(K135,M135,O135,Q135,S135,U135)</f>
         <v/>
       </c>
       <c r="C135" t="inlineStr">
@@ -18041,7 +19005,7 @@
     </row>
     <row r="136">
       <c r="A136" s="1">
-        <f>SUM(K136,M136,O136,Q136,S136)</f>
+        <f>SUM(K136,M136,O136,Q136,S136,U136)</f>
         <v/>
       </c>
       <c r="C136" t="inlineStr">
@@ -18088,7 +19052,7 @@
     </row>
     <row r="137">
       <c r="A137" s="1">
-        <f>SUM(K137,M137,O137,Q137,S137)</f>
+        <f>SUM(K137,M137,O137,Q137,S137,U137)</f>
         <v/>
       </c>
       <c r="C137" t="inlineStr">
@@ -18141,7 +19105,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1">
-        <f>SUM(K138,M138,O138,Q138,S138)</f>
+        <f>SUM(K138,M138,O138,Q138,S138,U138)</f>
         <v/>
       </c>
       <c r="C138" t="inlineStr">
@@ -18188,7 +19152,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1">
-        <f>SUM(K139,M139,O139,Q139,S139)</f>
+        <f>SUM(K139,M139,O139,Q139,S139,U139)</f>
         <v/>
       </c>
       <c r="C139" t="inlineStr">
@@ -18235,7 +19199,7 @@
     </row>
     <row r="140">
       <c r="A140" s="1">
-        <f>SUM(K140,M140,O140,Q140,S140)</f>
+        <f>SUM(K140,M140,O140,Q140,S140,U140)</f>
         <v/>
       </c>
       <c r="C140" t="inlineStr">
@@ -18282,7 +19246,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1">
-        <f>SUM(K141,M141,O141,Q141,S141)</f>
+        <f>SUM(K141,M141,O141,Q141,S141,U141)</f>
         <v/>
       </c>
       <c r="C141" t="inlineStr">
@@ -18329,7 +19293,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1">
-        <f>SUM(K142,M142,O142,Q142,S142)</f>
+        <f>SUM(K142,M142,O142,Q142,S142,U142)</f>
         <v/>
       </c>
       <c r="C142" t="inlineStr">
@@ -18376,7 +19340,7 @@
     </row>
     <row r="143">
       <c r="A143" s="1">
-        <f>SUM(K143,M143,O143,Q143,S143)</f>
+        <f>SUM(K143,M143,O143,Q143,S143,U143)</f>
         <v/>
       </c>
       <c r="C143" t="inlineStr">
@@ -18423,7 +19387,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1">
-        <f>SUM(K144,M144,O144,Q144,S144)</f>
+        <f>SUM(K144,M144,O144,Q144,S144,U144)</f>
         <v/>
       </c>
       <c r="C144" t="inlineStr">
@@ -18470,7 +19434,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1">
-        <f>SUM(K145,M145,O145,Q145,S145)</f>
+        <f>SUM(K145,M145,O145,Q145,S145,U145)</f>
         <v/>
       </c>
       <c r="C145" t="inlineStr">
@@ -18517,7 +19481,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1">
-        <f>SUM(K146,M146,O146,Q146,S146)</f>
+        <f>SUM(K146,M146,O146,Q146,S146,U146)</f>
         <v/>
       </c>
       <c r="C146" t="inlineStr">
@@ -18564,7 +19528,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1">
-        <f>SUM(K147,M147,O147,Q147,S147)</f>
+        <f>SUM(K147,M147,O147,Q147,S147,U147)</f>
         <v/>
       </c>
       <c r="C147" t="inlineStr">
@@ -18611,7 +19575,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1">
-        <f>SUM(K148,M148,O148,Q148,S148)</f>
+        <f>SUM(K148,M148,O148,Q148,S148,U148)</f>
         <v/>
       </c>
       <c r="C148" t="inlineStr">
@@ -18641,26 +19605,24 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Farmhouse Ranch Cheddar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K148" t="n">
+        <v>3.29</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1">
-        <f>SUM(K149,M149,O149,Q149,S149)</f>
+        <f>SUM(K149,M149,O149,Q149,S149,U149)</f>
         <v/>
       </c>
       <c r="C149" t="inlineStr">
@@ -18690,26 +19652,24 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Organic Kale</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K149" t="n">
+        <v>3.19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1">
-        <f>SUM(K150,M150,O150,Q150,S150)</f>
+        <f>SUM(K150,M150,O150,Q150,S150,U150)</f>
         <v/>
       </c>
       <c r="C150" t="inlineStr">
@@ -18739,26 +19699,24 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Pink Lady Apple</t>
+          <t>Pink Lady Apples</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K150" t="n">
+        <v>3.69</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1">
-        <f>SUM(K151,M151,O151,Q151,S151)</f>
+        <f>SUM(K151,M151,O151,Q151,S151,U151)</f>
         <v/>
       </c>
       <c r="C151" t="inlineStr">
@@ -18788,26 +19746,24 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Little Yellow Potatoes</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K151" t="n">
+        <v>3.29</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1">
-        <f>SUM(K152,M152,O152,Q152,S152)</f>
+        <f>SUM(K152,M152,O152,Q152,S152,U152)</f>
         <v/>
       </c>
       <c r="C152" t="inlineStr">
@@ -18837,26 +19793,24 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Multi-Peppers 3</t>
+          <t>Multi-Color Peppers, 3-Pack</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K152" t="n">
+        <v>2.69</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1">
-        <f>SUM(K153,M153,O153,Q153,S153)</f>
+        <f>SUM(K153,M153,O153,Q153,S153,U153)</f>
         <v/>
       </c>
       <c r="C153" t="inlineStr">
@@ -18886,26 +19840,24 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Green Grapes</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K153" t="n">
+        <v>3.81</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1">
-        <f>SUM(K154,M154,O154,Q154,S154)</f>
+        <f>SUM(K154,M154,O154,Q154,S154,U154)</f>
         <v/>
       </c>
       <c r="C154" t="inlineStr">
@@ -18935,26 +19887,24 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Mandarins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K154" t="n">
+        <v>2.89</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1">
-        <f>SUM(K155,M155,O155,Q155,S155)</f>
+        <f>SUM(K155,M155,O155,Q155,S155,U155)</f>
         <v/>
       </c>
       <c r="C155" t="inlineStr">
@@ -18984,26 +19934,24 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Organic Celery Hearts</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K155" t="n">
+        <v>2.59</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1">
-        <f>SUM(K156,M156,O156,Q156,S156)</f>
+        <f>SUM(K156,M156,O156,Q156,S156,U156)</f>
         <v/>
       </c>
       <c r="C156" t="inlineStr">
@@ -19033,26 +19981,24 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Head &amp; Shoulders</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K156" t="n">
+        <v>6.97</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1">
-        <f>SUM(K157,M157,O157,Q157,S157)</f>
+        <f>SUM(K157,M157,O157,Q157,S157,U157)</f>
         <v/>
       </c>
       <c r="C157" t="inlineStr">
@@ -19082,26 +20028,24 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Salt Grinder</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Seasonings &amp; Spices</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K157" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1">
-        <f>SUM(K158,M158,O158,Q158,S158)</f>
+        <f>SUM(K158,M158,O158,Q158,S158,U158)</f>
         <v/>
       </c>
       <c r="C158" t="inlineStr">
@@ -19131,26 +20075,24 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Peppercorn Grind</t>
+          <t>Peppercorn Grinder</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Seasonings &amp; Spices</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K158" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1">
-        <f>SUM(K159,M159,O159,Q159,S159)</f>
+        <f>SUM(K159,M159,O159,Q159,S159,U159)</f>
         <v/>
       </c>
       <c r="C159" t="inlineStr">
@@ -19180,26 +20122,24 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Broccoli Crowns</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K159" t="n">
+        <v>3.95</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1">
-        <f>SUM(K160,M160,O160,Q160,S160)</f>
+        <f>SUM(K160,M160,O160,Q160,S160,U160)</f>
         <v/>
       </c>
       <c r="C160" t="inlineStr">
@@ -19229,26 +20169,24 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K160" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1">
-        <f>SUM(K161,M161,O161,Q161,S161)</f>
+        <f>SUM(K161,M161,O161,Q161,S161,U161)</f>
         <v/>
       </c>
       <c r="C161" t="inlineStr">
@@ -19278,26 +20216,24 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Blueberries</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K161" t="n">
+        <v>5.98</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1">
-        <f>SUM(K162,M162,O162,Q162,S162)</f>
+        <f>SUM(K162,M162,O162,Q162,S162,U162)</f>
         <v/>
       </c>
       <c r="C162" t="inlineStr">
@@ -19327,26 +20263,24 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Raspberries</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K162" t="n">
+        <v>2.69</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1">
-        <f>SUM(K163,M163,O163,Q163,S163)</f>
+        <f>SUM(K163,M163,O163,Q163,S163,U163)</f>
         <v/>
       </c>
       <c r="C163" t="inlineStr">
@@ -19376,26 +20310,24 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Strawberries</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K163" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1">
-        <f>SUM(K164,M164,O164,Q164,S164)</f>
+        <f>SUM(K164,M164,O164,Q164,S164,U164)</f>
         <v/>
       </c>
       <c r="C164" t="inlineStr">
@@ -19425,26 +20357,24 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Gluten-Free Wide Pan Bread</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K164" t="n">
+        <v>6.79</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1">
-        <f>SUM(K165,M165,O165,Q165,S165)</f>
+        <f>SUM(K165,M165,O165,Q165,S165,U165)</f>
         <v/>
       </c>
       <c r="C165" t="inlineStr">
@@ -19474,26 +20404,24 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Artisanal Buns</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K165" t="n">
+        <v>2.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1">
-        <f>SUM(K166,M166,O166,Q166,S166)</f>
+        <f>SUM(K166,M166,O166,Q166,S166,U166)</f>
         <v/>
       </c>
       <c r="C166" t="inlineStr">
@@ -19523,26 +20451,24 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Organic Chickpeas</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Canned Beans &amp; Legumes</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="K166" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1">
-        <f>SUM(K167,M167,O167,Q167,S167)</f>
+        <f>SUM(K167,M167,O167,Q167,S167,U167)</f>
         <v/>
       </c>
       <c r="C167" t="inlineStr">
@@ -19572,26 +20498,1648 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pillsbury Flaky Biscuits</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Refrigerated Dough</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="K167" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1">
+        <f>SUM(K168,M168,O168,Q168,S168,U168)</f>
+        <v/>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>383249</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Deli Sliced CoJack</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Deli-Sliced Colby Jack Cheese</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Cheese</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K168" s="1" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1">
+        <f>SUM(K169,M169,O169,Q169,S169,U169)</f>
+        <v/>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>383252</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Deli Sliced Cheese</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Deli-Sliced Cheese</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Cheese</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K169" s="1" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1">
+        <f>SUM(K170,M170,O170,Q170,S170,U170)</f>
+        <v/>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>382473</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Shredded Mozz</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Shredded Mozzarella Cheese</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Cheese</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K170" s="1" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1">
+        <f>SUM(K171,M171,O171,Q171,S171,U171)</f>
+        <v/>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>380809</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2 Roll Paper Towel</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Paper Towels, 2-Roll</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Paper Towels</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K171" s="1" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1">
+        <f>SUM(K172,M172,O172,Q172,S172,U172)</f>
+        <v/>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>344280</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Cauli Crust Pizza</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Cauliflower Crust Pizza</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Frozen Pizza</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K172" s="1" t="n">
+        <v>8.289999999999999</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1">
+        <f>SUM(K173,M173,O173,Q173,S173,U173)</f>
+        <v/>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>272135</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Salmon Portions</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Salmon Portions</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Fresh Seafood</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K173" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1">
+        <f>SUM(K174,M174,O174,Q174,S174,U174)</f>
+        <v/>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>388137</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Large Eggs</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Large Eggs</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Eggs</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K174" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1">
+        <f>SUM(K175,M175,O175,Q175,S175,U175)</f>
+        <v/>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Fees &amp; Charges</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1">
+        <f>SUM(K176,M176,O176,Q176,S176,U176)</f>
+        <v/>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>TAQUITOS BLACK BEAN &amp; CH</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Black Bean &amp; Cheese Taquitos</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Frozen Appetizers</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K176" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1">
+        <f>SUM(K177,M177,O177,Q177,S177,U177)</f>
+        <v/>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>EMPIRE KOSHER TRKY HALF</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Empire Kosher Turkey Half</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K177" t="n">
+        <v>19.16</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1">
+        <f>SUM(K178,M178,O178,Q178,S178,U178)</f>
+        <v/>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>EMPIRE KOSHER BNL/SKNL B</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Empire Kosher Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K178" s="1" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="M178" s="1" t="n">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1">
+        <f>SUM(K179,M179,O179,Q179,S179,U179)</f>
+        <v/>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>BEEF KOSHER GROUND 85/15</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Kosher Ground Beef 85/15</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Fresh Beef</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K179" s="1" t="n">
+        <v>35.97</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1">
+        <f>SUM(K180,M180,O180,Q180,S180,U180)</f>
+        <v/>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>CHOCOLATE BABKA</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Chocolate Babka</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K180" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1">
+        <f>SUM(K181,M181,O181,Q181,S181,U181)</f>
+        <v/>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>R-SALAD COMPLETE SWEET K</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Complete Sweet Kale Salad Kit</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Salad Kits</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K181" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1">
+        <f>SUM(K182,M182,O182,Q182,S182,U182)</f>
+        <v/>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>HALF MOON  COOKIES</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Half Moon Cookies</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Cookies</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K182" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1">
+        <f>SUM(K183,M183,O183,Q183,S183,U183)</f>
+        <v/>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HOL PUMPKIN CREAM CHEESE </t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Pumpkin Cream Cheese</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Cream Cheese</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K183" t="n">
+        <v>2.79</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S167"/>
+  <autoFilter ref="A1:U181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BC49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" style="84" min="1" max="1"/>
+    <col width="48" customWidth="1" style="84" min="2" max="2"/>
+    <col width="6" customWidth="1" style="84" min="10" max="10"/>
+    <col width="28" customWidth="1" style="84" min="11" max="11"/>
+    <col width="14" customWidth="1" style="84" min="12" max="12"/>
+    <col width="16" customWidth="1" style="84" min="28" max="28"/>
+    <col width="16" customWidth="1" style="84" min="29" max="29"/>
+    <col width="16" customWidth="1" style="84" min="30" max="30"/>
+    <col width="16" customWidth="1" style="84" min="31" max="31"/>
+    <col width="16" customWidth="1" style="84" min="32" max="32"/>
+    <col width="16" customWidth="1" style="84" min="33" max="33"/>
+    <col width="16" customWidth="1" style="84" min="34" max="34"/>
+    <col width="16" customWidth="1" style="84" min="35" max="35"/>
+    <col width="16" customWidth="1" style="84" min="36" max="36"/>
+    <col width="16" customWidth="1" style="84" min="37" max="37"/>
+    <col width="16" customWidth="1" style="84" min="38" max="38"/>
+    <col width="16" customWidth="1" style="84" min="39" max="39"/>
+    <col width="16" customWidth="1" style="84" min="40" max="40"/>
+    <col width="16" customWidth="1" style="84" min="41" max="41"/>
+    <col width="16" customWidth="1" style="84" min="42" max="42"/>
+    <col width="16" customWidth="1" style="84" min="43" max="43"/>
+    <col width="16" customWidth="1" style="84" min="44" max="44"/>
+    <col width="16" customWidth="1" style="84" min="45" max="45"/>
+    <col width="16" customWidth="1" style="84" min="46" max="46"/>
+    <col width="16" customWidth="1" style="84" min="47" max="47"/>
+    <col width="16" customWidth="1" style="84" min="48" max="48"/>
+    <col width="16" customWidth="1" style="84" min="49" max="49"/>
+    <col width="16" customWidth="1" style="84" min="50" max="50"/>
+    <col width="16" customWidth="1" style="84" min="51" max="51"/>
+    <col width="16" customWidth="1" style="84" min="52" max="52"/>
+    <col width="16" customWidth="1" style="84" min="53" max="53"/>
+    <col width="16" customWidth="1" style="84" min="54" max="54"/>
+    <col width="16" customWidth="1" style="84" min="55" max="55"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="106" t="inlineStr">
+        <is>
+          <t>9_26w2</t>
+        </is>
+      </c>
+      <c r="AB1" s="107" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="107" t="inlineStr">
+        <is>
+          <t>Ideal Remaining Budget</t>
+        </is>
+      </c>
+      <c r="AD1" s="107" t="inlineStr">
+        <is>
+          <t>Actual Remaining Budget</t>
+        </is>
+      </c>
+      <c r="AE1" s="107" t="inlineStr">
+        <is>
+          <t>Cumulative Spending</t>
+        </is>
+      </c>
+      <c r="AG1" s="107" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="AH1" s="107" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="AI1" s="107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK1" s="107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL1" s="107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM1" s="107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN1" s="107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO1" s="107" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AP1" s="107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ1" s="107" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AR1" s="107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AS1" s="107" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AT1" s="107" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AU1" s="107" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AV1" s="107" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AW1" s="107" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AX1" s="107" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AY1" s="107" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AZ1" s="107" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BA1" s="107" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BB1" s="107" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BC1" s="107" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="AB2" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="AC2" s="132" t="n">
+        <v>326</v>
+      </c>
+      <c r="AD2" s="132" t="n">
+        <v>228.87</v>
+      </c>
+      <c r="AE2" s="132" t="n">
+        <v>97.13000000000001</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="AH2" s="132" t="n">
+        <v>326</v>
+      </c>
+      <c r="AI2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="109" t="inlineStr">
+        <is>
+          <t>Budget Plan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9_26w2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="AC3" s="132" t="n">
+        <v>271.6666666666667</v>
+      </c>
+      <c r="AD3" s="132" t="n">
+        <v>103.29</v>
+      </c>
+      <c r="AE3" s="132" t="n">
+        <v>222.71</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Spent</t>
+        </is>
+      </c>
+      <c r="AH3" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="132" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="AK3" s="132" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AL3" s="132" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="AM3" s="132" t="n">
+        <v>6.960000000000001</v>
+      </c>
+      <c r="AN3" s="132" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AO3" s="132" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AP3" s="132" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ3" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="132" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AS3" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="132" t="n">
+        <v>104.83</v>
+      </c>
+      <c r="AU3" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="132" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AW3" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="132" t="n">
+        <v>42.20999999999999</v>
+      </c>
+      <c r="AZ3" s="132" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="BA3" s="132" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BB3" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="109" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="AC4" s="132" t="n">
+        <v>217.3333333333334</v>
+      </c>
+      <c r="AD4" s="132" t="n">
+        <v>103.29</v>
+      </c>
+      <c r="AE4" s="132" t="n">
+        <v>222.71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="109" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="AC5" s="132" t="n">
+        <v>163</v>
+      </c>
+      <c r="AD5" s="132" t="n">
+        <v>103.29</v>
+      </c>
+      <c r="AE5" s="132" t="n">
+        <v>222.71</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="109" t="inlineStr">
+        <is>
+          <t>Category Scope</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>All Categories</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="AC6" s="132" t="n">
+        <v>108.6666666666667</v>
+      </c>
+      <c r="AD6" s="132" t="n">
+        <v>103.29</v>
+      </c>
+      <c r="AE6" s="132" t="n">
+        <v>222.71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="109" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>All Categories</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="AC7" s="132" t="n">
+        <v>54.33333333333332</v>
+      </c>
+      <c r="AD7" s="132" t="n">
+        <v>103.29</v>
+      </c>
+      <c r="AE7" s="132" t="n">
+        <v>222.71</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="109" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="B8" s="132" t="n">
+        <v>326</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="AC8" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="132" t="n">
+        <v>103.29</v>
+      </c>
+      <c r="AE8" s="132" t="n">
+        <v>222.71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="109" t="inlineStr">
+        <is>
+          <t>Total Spent</t>
+        </is>
+      </c>
+      <c r="B9" s="132" t="n">
+        <v>222.71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="109" t="inlineStr">
+        <is>
+          <t>Remaining Budget</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>103.29</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="109" t="inlineStr">
+        <is>
+          <t>Relevant Date</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="109" t="inlineStr">
+        <is>
+          <t>Ideal Spending Through Relevant Date</t>
+        </is>
+      </c>
+      <c r="B12" s="132" t="n">
+        <v>54.33333333333331</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="109" t="inlineStr">
+        <is>
+          <t>Actual Spending Through Relevant Date</t>
+        </is>
+      </c>
+      <c r="B13" s="132" t="n">
+        <v>222.71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="109" t="inlineStr">
+        <is>
+          <t>Ahead / Behind Budget</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Behind by $168.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="110" t="inlineStr">
+        <is>
+          <t>Budget vs Category Spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="J18" s="111" t="inlineStr">
+        <is>
+          <t>Category Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="J19" s="107" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="K19" s="107" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="L19" s="107" t="inlineStr">
+        <is>
+          <t>Spent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="J20" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Baby Care</t>
+        </is>
+      </c>
+      <c r="L20" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="J21" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="L21" s="132" t="n">
+        <v>15.77</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="J22" s="114" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Condiments &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="L22" s="132" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="J23" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="L23" s="132" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="J24" s="116" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+      <c r="L24" s="132" t="n">
+        <v>6.960000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="J25" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Eggs</t>
+        </is>
+      </c>
+      <c r="L25" s="132" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="J26" s="118" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="L26" s="132" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="J27" s="119" t="n">
+        <v>8</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="L27" s="132" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="J28" s="120" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="L28" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="J29" s="121" t="n">
+        <v>10</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Frozen Food</t>
+        </is>
+      </c>
+      <c r="L29" s="132" t="n">
+        <v>12.78</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="J30" s="122" t="n">
+        <v>11</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Home Improvement</t>
+        </is>
+      </c>
+      <c r="L30" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="J31" s="123" t="n">
+        <v>12</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Meat</t>
+        </is>
+      </c>
+      <c r="L31" s="132" t="n">
+        <v>104.83</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="J32" s="124" t="n">
+        <v>13</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="L32" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="J33" s="125" t="n">
+        <v>14</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="L33" s="132" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="J34" s="126" t="n">
+        <v>15</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="L34" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="J35" s="127" t="n">
+        <v>16</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Prepared Eating</t>
+        </is>
+      </c>
+      <c r="L35" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="J36" s="128" t="n">
+        <v>17</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="L36" s="132" t="n">
+        <v>42.20999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="J37" s="129" t="n">
+        <v>18</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="L37" s="132" t="n">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="J38" s="130" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Toiletries, Cleaning and Disposables</t>
+        </is>
+      </c>
+      <c r="L38" s="132" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="J39" s="131" t="n">
+        <v>20</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Torah</t>
+        </is>
+      </c>
+      <c r="L39" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="J40" s="112" t="n">
+        <v>21</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Wine</t>
+        </is>
+      </c>
+      <c r="L40" s="132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="83" t="inlineStr">
+        <is>
+          <t>Interpretation: the chart has exactly two bars. Budget is the full configured Budget Plan amount. Spent is one stacked bar; each colored segment is the amount spent in one Category through the Relevant Date. The number inside a segment matches the Category Key on the right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="A47:H49"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19601,7 +22149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:S69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="84" min="1" max="1"/>
@@ -19620,6 +22168,9 @@
     <col width="34" customWidth="1" style="84" min="14" max="14"/>
     <col width="34" customWidth="1" style="84" min="15" max="15"/>
     <col width="34" customWidth="1" style="84" min="16" max="16"/>
+    <col width="34" customWidth="1" style="84" min="17" max="17"/>
+    <col width="34" customWidth="1" style="84" min="18" max="18"/>
+    <col width="34" customWidth="1" style="84" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" s="84">
@@ -19701,6 +22252,21 @@
       <c r="P1" s="93" t="inlineStr">
         <is>
           <t>Product 14</t>
+        </is>
+      </c>
+      <c r="Q1" s="93" t="inlineStr">
+        <is>
+          <t>Product 15</t>
+        </is>
+      </c>
+      <c r="R1" s="93" t="inlineStr">
+        <is>
+          <t>Product 16</t>
+        </is>
+      </c>
+      <c r="S1" s="93" t="inlineStr">
+        <is>
+          <t>Product 17</t>
         </is>
       </c>
     </row>
@@ -19733,6 +22299,9 @@
       <c r="N2" s="95" t="n"/>
       <c r="O2" s="95" t="n"/>
       <c r="P2" s="95" t="n"/>
+      <c r="Q2" s="95" t="n"/>
+      <c r="R2" s="95" t="n"/>
+      <c r="S2" s="95" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1" s="84">
       <c r="A3" s="96" t="inlineStr">
@@ -19779,6 +22348,9 @@
       <c r="N3" s="97" t="n"/>
       <c r="O3" s="97" t="n"/>
       <c r="P3" s="97" t="n"/>
+      <c r="Q3" s="97" t="n"/>
+      <c r="R3" s="97" t="n"/>
+      <c r="S3" s="97" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1" s="84">
       <c r="A4" s="98" t="inlineStr">
@@ -19817,6 +22389,9 @@
       <c r="N4" s="99" t="n"/>
       <c r="O4" s="99" t="n"/>
       <c r="P4" s="99" t="n"/>
+      <c r="Q4" s="99" t="n"/>
+      <c r="R4" s="99" t="n"/>
+      <c r="S4" s="99" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1" s="84">
       <c r="A5" s="100" t="inlineStr">
@@ -19851,6 +22426,9 @@
       <c r="N5" s="101" t="n"/>
       <c r="O5" s="101" t="n"/>
       <c r="P5" s="101" t="n"/>
+      <c r="Q5" s="101" t="n"/>
+      <c r="R5" s="101" t="n"/>
+      <c r="S5" s="101" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1" s="84">
       <c r="A6" s="102" t="inlineStr">
@@ -19881,6 +22459,9 @@
       <c r="N6" s="103" t="n"/>
       <c r="O6" s="103" t="n"/>
       <c r="P6" s="103" t="n"/>
+      <c r="Q6" s="103" t="n"/>
+      <c r="R6" s="103" t="n"/>
+      <c r="S6" s="103" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1" s="84">
       <c r="A7" s="104" t="inlineStr">
@@ -19895,25 +22476,29 @@
       </c>
       <c r="C7" s="105" t="inlineStr">
         <is>
+          <t>Artisanal Buns</t>
+        </is>
+      </c>
+      <c r="D7" s="105" t="inlineStr">
+        <is>
           <t>Dave's Killer Bread Oats &amp; Blues</t>
         </is>
       </c>
-      <c r="D7" s="105" t="inlineStr">
+      <c r="E7" s="105" t="inlineStr">
         <is>
           <t>Dave's Killer Bread Organic Oats &amp; Blues</t>
         </is>
       </c>
-      <c r="E7" s="105" t="inlineStr">
+      <c r="F7" s="105" t="inlineStr">
         <is>
           <t>Gluten-Free Wide Pan Bread</t>
         </is>
       </c>
-      <c r="F7" s="105" t="inlineStr">
+      <c r="G7" s="105" t="inlineStr">
         <is>
           <t>No [or possibly Nature's Own] Honey Wheat Bread</t>
         </is>
       </c>
-      <c r="G7" s="105" t="n"/>
       <c r="H7" s="105" t="n"/>
       <c r="I7" s="105" t="n"/>
       <c r="J7" s="105" t="n"/>
@@ -19923,6 +22508,9 @@
       <c r="N7" s="105" t="n"/>
       <c r="O7" s="105" t="n"/>
       <c r="P7" s="105" t="n"/>
+      <c r="Q7" s="105" t="n"/>
+      <c r="R7" s="105" t="n"/>
+      <c r="S7" s="105" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1" s="84">
       <c r="A8" s="94" t="inlineStr">
@@ -19957,6 +22545,9 @@
       <c r="N8" s="95" t="n"/>
       <c r="O8" s="95" t="n"/>
       <c r="P8" s="95" t="n"/>
+      <c r="Q8" s="95" t="n"/>
+      <c r="R8" s="95" t="n"/>
+      <c r="S8" s="95" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1" s="84">
       <c r="A9" s="96" t="inlineStr">
@@ -19987,6 +22578,9 @@
       <c r="N9" s="97" t="n"/>
       <c r="O9" s="97" t="n"/>
       <c r="P9" s="97" t="n"/>
+      <c r="Q9" s="97" t="n"/>
+      <c r="R9" s="97" t="n"/>
+      <c r="S9" s="97" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1" s="84">
       <c r="A10" s="98" t="inlineStr">
@@ -20004,10 +22598,26 @@
           <t>Cabot Mexican Shredded Cheese</t>
         </is>
       </c>
-      <c r="D10" s="99" t="n"/>
-      <c r="E10" s="99" t="n"/>
-      <c r="F10" s="99" t="n"/>
-      <c r="G10" s="99" t="n"/>
+      <c r="D10" s="99" t="inlineStr">
+        <is>
+          <t>Deli-Sliced Cheese</t>
+        </is>
+      </c>
+      <c r="E10" s="99" t="inlineStr">
+        <is>
+          <t>Deli-Sliced Colby Jack Cheese</t>
+        </is>
+      </c>
+      <c r="F10" s="99" t="inlineStr">
+        <is>
+          <t>Farmhouse Ranch Cheddar</t>
+        </is>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Shredded Mozzarella Cheese</t>
+        </is>
+      </c>
       <c r="H10" s="99" t="n"/>
       <c r="I10" s="99" t="n"/>
       <c r="J10" s="99" t="n"/>
@@ -20017,6 +22627,9 @@
       <c r="N10" s="99" t="n"/>
       <c r="O10" s="99" t="n"/>
       <c r="P10" s="99" t="n"/>
+      <c r="Q10" s="99" t="n"/>
+      <c r="R10" s="99" t="n"/>
+      <c r="S10" s="99" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1" s="84">
       <c r="A11" s="100" t="inlineStr">
@@ -20047,21 +22660,24 @@
       <c r="N11" s="101" t="n"/>
       <c r="O11" s="101" t="n"/>
       <c r="P11" s="101" t="n"/>
+      <c r="Q11" s="101" t="n"/>
+      <c r="R11" s="101" t="n"/>
+      <c r="S11" s="101" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1" s="84">
       <c r="A12" s="102" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="B12" s="102" t="inlineStr">
         <is>
-          <t>Crackers</t>
+          <t>Cookies</t>
         </is>
       </c>
       <c r="C12" s="103" t="inlineStr">
         <is>
-          <t>Peanut Butter Toast Crackers</t>
+          <t>Half Moon Cookies</t>
         </is>
       </c>
       <c r="D12" s="103" t="n"/>
@@ -20077,21 +22693,24 @@
       <c r="N12" s="103" t="n"/>
       <c r="O12" s="103" t="n"/>
       <c r="P12" s="103" t="n"/>
+      <c r="Q12" s="103" t="n"/>
+      <c r="R12" s="103" t="n"/>
+      <c r="S12" s="103" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1" s="84">
       <c r="A13" s="104" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="B13" s="104" t="inlineStr">
         <is>
-          <t>Cream &amp; Half-and-Half</t>
+          <t>Crackers</t>
         </is>
       </c>
       <c r="C13" s="105" t="inlineStr">
         <is>
-          <t>Publix Half &amp; Half, Half Gallon</t>
+          <t>Peanut Butter Toast Crackers</t>
         </is>
       </c>
       <c r="D13" s="105" t="n"/>
@@ -20107,21 +22726,24 @@
       <c r="N13" s="105" t="n"/>
       <c r="O13" s="105" t="n"/>
       <c r="P13" s="105" t="n"/>
+      <c r="Q13" s="105" t="n"/>
+      <c r="R13" s="105" t="n"/>
+      <c r="S13" s="105" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1" s="84">
       <c r="A14" s="94" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B14" s="94" t="inlineStr">
         <is>
-          <t>Croutons</t>
+          <t>Cream &amp; Half-and-Half</t>
         </is>
       </c>
       <c r="C14" s="95" t="inlineStr">
         <is>
-          <t>Organic Croutons</t>
+          <t>Publix Half &amp; Half, Half Gallon</t>
         </is>
       </c>
       <c r="D14" s="95" t="n"/>
@@ -20137,21 +22759,24 @@
       <c r="N14" s="95" t="n"/>
       <c r="O14" s="95" t="n"/>
       <c r="P14" s="95" t="n"/>
+      <c r="Q14" s="95" t="n"/>
+      <c r="R14" s="95" t="n"/>
+      <c r="S14" s="95" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1" s="84">
       <c r="A15" s="96" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B15" s="96" t="inlineStr">
         <is>
-          <t>Deli Meat</t>
+          <t>Cream Cheese</t>
         </is>
       </c>
       <c r="C15" s="97" t="inlineStr">
         <is>
-          <t>Hillshire Farm Oven Roasted Turkey Breast</t>
+          <t>Pumpkin Cream Cheese</t>
         </is>
       </c>
       <c r="D15" s="97" t="n"/>
@@ -20167,21 +22792,24 @@
       <c r="N15" s="97" t="n"/>
       <c r="O15" s="97" t="n"/>
       <c r="P15" s="97" t="n"/>
+      <c r="Q15" s="97" t="n"/>
+      <c r="R15" s="97" t="n"/>
+      <c r="S15" s="97" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1" s="84">
       <c r="A16" s="98" t="inlineStr">
         <is>
-          <t>Toiletries, Cleaning and Disposables</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="B16" s="98" t="inlineStr">
         <is>
-          <t>Deodorant</t>
+          <t>Croutons</t>
         </is>
       </c>
       <c r="C16" s="99" t="inlineStr">
         <is>
-          <t>Dove Men+Care Antiperspirant</t>
+          <t>Organic Croutons</t>
         </is>
       </c>
       <c r="D16" s="99" t="n"/>
@@ -20197,21 +22825,24 @@
       <c r="N16" s="99" t="n"/>
       <c r="O16" s="99" t="n"/>
       <c r="P16" s="99" t="n"/>
+      <c r="Q16" s="99" t="n"/>
+      <c r="R16" s="99" t="n"/>
+      <c r="S16" s="99" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="84">
       <c r="A17" s="100" t="inlineStr">
         <is>
-          <t>Condiments &amp; Seasonings</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="B17" s="100" t="inlineStr">
         <is>
-          <t>Dips &amp; Spreads</t>
+          <t>Deli Meat</t>
         </is>
       </c>
       <c r="C17" s="101" t="inlineStr">
         <is>
-          <t>Hummus Mini Cups</t>
+          <t>Hillshire Farm Oven Roasted Turkey Breast</t>
         </is>
       </c>
       <c r="D17" s="101" t="n"/>
@@ -20227,6 +22858,9 @@
       <c r="N17" s="101" t="n"/>
       <c r="O17" s="101" t="n"/>
       <c r="P17" s="101" t="n"/>
+      <c r="Q17" s="101" t="n"/>
+      <c r="R17" s="101" t="n"/>
+      <c r="S17" s="101" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1" s="84">
       <c r="A18" s="102" t="inlineStr">
@@ -20236,12 +22870,12 @@
       </c>
       <c r="B18" s="102" t="inlineStr">
         <is>
-          <t>Dishwashing Supplies</t>
+          <t>Deodorant</t>
         </is>
       </c>
       <c r="C18" s="103" t="inlineStr">
         <is>
-          <t>Dawn Dish Cleaning Brush Wand</t>
+          <t>Dove Men+Care Antiperspirant</t>
         </is>
       </c>
       <c r="D18" s="103" t="n"/>
@@ -20257,21 +22891,24 @@
       <c r="N18" s="103" t="n"/>
       <c r="O18" s="103" t="n"/>
       <c r="P18" s="103" t="n"/>
+      <c r="Q18" s="103" t="n"/>
+      <c r="R18" s="103" t="n"/>
+      <c r="S18" s="103" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1" s="84">
       <c r="A19" s="104" t="inlineStr">
         <is>
-          <t>Toiletries, Cleaning and Disposables</t>
+          <t>Condiments &amp; Seasonings</t>
         </is>
       </c>
       <c r="B19" s="104" t="inlineStr">
         <is>
-          <t>Disposable Tableware</t>
+          <t>Dips &amp; Spreads</t>
         </is>
       </c>
       <c r="C19" s="105" t="inlineStr">
         <is>
-          <t>Everyday Paper Plates, 8.5 Inch</t>
+          <t>Hummus Mini Cups</t>
         </is>
       </c>
       <c r="D19" s="105" t="n"/>
@@ -20287,21 +22924,24 @@
       <c r="N19" s="105" t="n"/>
       <c r="O19" s="105" t="n"/>
       <c r="P19" s="105" t="n"/>
+      <c r="Q19" s="105" t="n"/>
+      <c r="R19" s="105" t="n"/>
+      <c r="S19" s="105" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1" s="84">
       <c r="A20" s="94" t="inlineStr">
         <is>
-          <t>Eggs</t>
+          <t>Toiletries, Cleaning and Disposables</t>
         </is>
       </c>
       <c r="B20" s="94" t="inlineStr">
         <is>
-          <t>Eggs</t>
+          <t>Dishwashing Supplies</t>
         </is>
       </c>
       <c r="C20" s="95" t="inlineStr">
         <is>
-          <t>Great Value Large White Eggs</t>
+          <t>Dawn Dish Cleaning Brush Wand</t>
         </is>
       </c>
       <c r="D20" s="95" t="n"/>
@@ -20317,48 +22957,31 @@
       <c r="N20" s="95" t="n"/>
       <c r="O20" s="95" t="n"/>
       <c r="P20" s="95" t="n"/>
+      <c r="Q20" s="95" t="n"/>
+      <c r="R20" s="95" t="n"/>
+      <c r="S20" s="95" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1" s="84">
       <c r="A21" s="96" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Toiletries, Cleaning and Disposables</t>
         </is>
       </c>
       <c r="B21" s="96" t="inlineStr">
         <is>
-          <t>Fees &amp; Charges</t>
+          <t>Disposable Tableware</t>
         </is>
       </c>
       <c r="C21" s="97" t="inlineStr">
         <is>
-          <t>Driver Tip</t>
-        </is>
-      </c>
-      <c r="D21" s="97" t="inlineStr">
-        <is>
-          <t>Express Delivery Fee</t>
-        </is>
-      </c>
-      <c r="E21" s="97" t="inlineStr">
-        <is>
-          <t>Price Adjustment</t>
-        </is>
-      </c>
-      <c r="F21" s="97" t="inlineStr">
-        <is>
-          <t>Sales Tax</t>
-        </is>
-      </c>
-      <c r="G21" s="97" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="H21" s="97" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
+          <t>Everyday Paper Plates, 8.5 Inch</t>
+        </is>
+      </c>
+      <c r="D21" s="97" t="n"/>
+      <c r="E21" s="97" t="n"/>
+      <c r="F21" s="97" t="n"/>
+      <c r="G21" s="97" t="n"/>
+      <c r="H21" s="97" t="n"/>
       <c r="I21" s="97" t="n"/>
       <c r="J21" s="97" t="n"/>
       <c r="K21" s="97" t="n"/>
@@ -20367,26 +22990,29 @@
       <c r="N21" s="97" t="n"/>
       <c r="O21" s="97" t="n"/>
       <c r="P21" s="97" t="n"/>
+      <c r="Q21" s="97" t="n"/>
+      <c r="R21" s="97" t="n"/>
+      <c r="S21" s="97" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="84">
       <c r="A22" s="98" t="inlineStr">
         <is>
-          <t>Toiletries, Cleaning and Disposables</t>
+          <t>Eggs</t>
         </is>
       </c>
       <c r="B22" s="98" t="inlineStr">
         <is>
-          <t>Food Storage</t>
+          <t>Eggs</t>
         </is>
       </c>
       <c r="C22" s="99" t="inlineStr">
         <is>
-          <t>Ziploc Gallon Freezer Bags</t>
+          <t>Great Value Large White Eggs</t>
         </is>
       </c>
       <c r="D22" s="99" t="inlineStr">
         <is>
-          <t>Ziploc Quart Freezer Bags</t>
+          <t>Large Eggs</t>
         </is>
       </c>
       <c r="E22" s="99" t="n"/>
@@ -20401,84 +23027,82 @@
       <c r="N22" s="99" t="n"/>
       <c r="O22" s="99" t="n"/>
       <c r="P22" s="99" t="n"/>
+      <c r="Q22" s="99" t="n"/>
+      <c r="R22" s="99" t="n"/>
+      <c r="S22" s="99" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="84">
       <c r="A23" s="100" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="B23" s="100" t="inlineStr">
         <is>
-          <t>Fresh Fruit</t>
+          <t>Fees &amp; Charges</t>
         </is>
       </c>
       <c r="C23" s="101" t="inlineStr">
         <is>
-          <t>Bananas</t>
+          <t>Driver Tip</t>
         </is>
       </c>
       <c r="D23" s="101" t="inlineStr">
         <is>
-          <t>Blueberries</t>
+          <t>Express Delivery Fee</t>
         </is>
       </c>
       <c r="E23" s="101" t="inlineStr">
         <is>
-          <t>Golden Kiwi</t>
+          <t>Price Adjustment</t>
         </is>
       </c>
       <c r="F23" s="101" t="inlineStr">
         <is>
-          <t>Mandarin Oranges</t>
+          <t>Sales Tax</t>
         </is>
       </c>
       <c r="G23" s="101" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="H23" s="101" t="inlineStr">
         <is>
-          <t>Persian Limes</t>
-        </is>
-      </c>
-      <c r="I23" s="101" t="inlineStr">
-        <is>
-          <t>Pink Lady Apples</t>
-        </is>
-      </c>
-      <c r="J23" s="101" t="inlineStr">
-        <is>
-          <t>Strawberries, 1 lb</t>
-        </is>
-      </c>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="I23" s="101" t="n"/>
+      <c r="J23" s="101" t="n"/>
       <c r="K23" s="101" t="n"/>
       <c r="L23" s="101" t="n"/>
       <c r="M23" s="101" t="n"/>
       <c r="N23" s="101" t="n"/>
       <c r="O23" s="101" t="n"/>
       <c r="P23" s="101" t="n"/>
+      <c r="Q23" s="101" t="n"/>
+      <c r="R23" s="101" t="n"/>
+      <c r="S23" s="101" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1" s="84">
       <c r="A24" s="102" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Toiletries, Cleaning and Disposables</t>
         </is>
       </c>
       <c r="B24" s="102" t="inlineStr">
         <is>
-          <t>Fresh Herbs</t>
+          <t>Food Storage</t>
         </is>
       </c>
       <c r="C24" s="103" t="inlineStr">
         <is>
-          <t>Cilantro</t>
+          <t>Ziploc Gallon Freezer Bags</t>
         </is>
       </c>
       <c r="D24" s="103" t="inlineStr">
         <is>
-          <t>Parsley</t>
+          <t>Ziploc Quart Freezer Bags</t>
         </is>
       </c>
       <c r="E24" s="103" t="n"/>
@@ -20493,6 +23117,9 @@
       <c r="N24" s="103" t="n"/>
       <c r="O24" s="103" t="n"/>
       <c r="P24" s="103" t="n"/>
+      <c r="Q24" s="103" t="n"/>
+      <c r="R24" s="103" t="n"/>
+      <c r="S24" s="103" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="84">
       <c r="A25" s="104" t="inlineStr">
@@ -20502,12 +23129,12 @@
       </c>
       <c r="B25" s="104" t="inlineStr">
         <is>
-          <t>Fresh Poultry</t>
+          <t>Fresh Beef</t>
         </is>
       </c>
       <c r="C25" s="105" t="inlineStr">
         <is>
-          <t>Empire Kosher Ground Turkey</t>
+          <t>Kosher Ground Beef 85/15</t>
         </is>
       </c>
       <c r="D25" s="105" t="n"/>
@@ -20523,40 +23150,86 @@
       <c r="N25" s="105" t="n"/>
       <c r="O25" s="105" t="n"/>
       <c r="P25" s="105" t="n"/>
+      <c r="Q25" s="105" t="n"/>
+      <c r="R25" s="105" t="n"/>
+      <c r="S25" s="105" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1" s="84">
       <c r="A26" s="94" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="B26" s="94" t="inlineStr">
         <is>
-          <t>Fresh Seafood</t>
+          <t>Fresh Fruit</t>
         </is>
       </c>
       <c r="C26" s="95" t="inlineStr">
         <is>
-          <t>GreenWise Keta Salmon Fillet</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="D26" s="95" t="inlineStr">
         <is>
-          <t>Salmon Fillet</t>
-        </is>
-      </c>
-      <c r="E26" s="95" t="n"/>
-      <c r="F26" s="95" t="n"/>
-      <c r="G26" s="95" t="n"/>
-      <c r="H26" s="95" t="n"/>
-      <c r="I26" s="95" t="n"/>
-      <c r="J26" s="95" t="n"/>
-      <c r="K26" s="95" t="n"/>
-      <c r="L26" s="95" t="n"/>
-      <c r="M26" s="95" t="n"/>
-      <c r="N26" s="95" t="n"/>
+          <t>Blueberries</t>
+        </is>
+      </c>
+      <c r="E26" s="95" t="inlineStr">
+        <is>
+          <t>Golden Kiwi</t>
+        </is>
+      </c>
+      <c r="F26" s="95" t="inlineStr">
+        <is>
+          <t>Green Grapes</t>
+        </is>
+      </c>
+      <c r="G26" s="95" t="inlineStr">
+        <is>
+          <t>Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="H26" s="95" t="inlineStr">
+        <is>
+          <t>Mandarins</t>
+        </is>
+      </c>
+      <c r="I26" s="95" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="J26" s="95" t="inlineStr">
+        <is>
+          <t>Persian Limes</t>
+        </is>
+      </c>
+      <c r="K26" s="95" t="inlineStr">
+        <is>
+          <t>Pink Lady Apples</t>
+        </is>
+      </c>
+      <c r="L26" s="95" t="inlineStr">
+        <is>
+          <t>Raspberries</t>
+        </is>
+      </c>
+      <c r="M26" s="95" t="inlineStr">
+        <is>
+          <t>Strawberries</t>
+        </is>
+      </c>
+      <c r="N26" s="95" t="inlineStr">
+        <is>
+          <t>Strawberries, 1 lb</t>
+        </is>
+      </c>
       <c r="O26" s="95" t="n"/>
       <c r="P26" s="95" t="n"/>
+      <c r="Q26" s="95" t="n"/>
+      <c r="R26" s="95" t="n"/>
+      <c r="S26" s="95" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1" s="84">
       <c r="A27" s="96" t="inlineStr">
@@ -20566,102 +23239,61 @@
       </c>
       <c r="B27" s="96" t="inlineStr">
         <is>
-          <t>Fresh Vegetables</t>
+          <t>Fresh Herbs</t>
         </is>
       </c>
       <c r="C27" s="97" t="inlineStr">
         <is>
-          <t>Baby Carrots</t>
+          <t>Cilantro</t>
         </is>
       </c>
       <c r="D27" s="97" t="inlineStr">
         <is>
-          <t>Beefsteak Tomatoes</t>
-        </is>
-      </c>
-      <c r="E27" s="97" t="inlineStr">
-        <is>
-          <t>Broccoli Crowns</t>
-        </is>
-      </c>
-      <c r="F27" s="97" t="inlineStr">
-        <is>
-          <t>Fresh Trimmed Green Beans</t>
-        </is>
-      </c>
-      <c r="G27" s="97" t="inlineStr">
-        <is>
-          <t>Green Beans</t>
-        </is>
-      </c>
-      <c r="H27" s="97" t="inlineStr">
-        <is>
-          <t>Medley Potatoes</t>
-        </is>
-      </c>
-      <c r="I27" s="97" t="inlineStr">
-        <is>
-          <t>Mini Cucumbers</t>
-        </is>
-      </c>
-      <c r="J27" s="97" t="inlineStr">
-        <is>
-          <t>Multi-Color Peppers, 3-Pack</t>
-        </is>
-      </c>
-      <c r="K27" s="97" t="inlineStr">
-        <is>
-          <t>Red Onion</t>
-        </is>
-      </c>
-      <c r="L27" s="97" t="inlineStr">
-        <is>
-          <t>Red Onions</t>
-        </is>
-      </c>
-      <c r="M27" s="97" t="inlineStr">
-        <is>
-          <t>Ruby Sensation Potato Nibbles</t>
-        </is>
-      </c>
-      <c r="N27" s="97" t="inlineStr">
-        <is>
-          <t>Tomatoes on the Vine</t>
-        </is>
-      </c>
-      <c r="O27" s="97" t="inlineStr">
-        <is>
-          <t>Yellow Squash</t>
-        </is>
-      </c>
-      <c r="P27" s="97" t="inlineStr">
-        <is>
-          <t>Zucchini</t>
-        </is>
-      </c>
+          <t>Parsley</t>
+        </is>
+      </c>
+      <c r="E27" s="97" t="n"/>
+      <c r="F27" s="97" t="n"/>
+      <c r="G27" s="97" t="n"/>
+      <c r="H27" s="97" t="n"/>
+      <c r="I27" s="97" t="n"/>
+      <c r="J27" s="97" t="n"/>
+      <c r="K27" s="97" t="n"/>
+      <c r="L27" s="97" t="n"/>
+      <c r="M27" s="97" t="n"/>
+      <c r="N27" s="97" t="n"/>
+      <c r="O27" s="97" t="n"/>
+      <c r="P27" s="97" t="n"/>
+      <c r="Q27" s="97" t="n"/>
+      <c r="R27" s="97" t="n"/>
+      <c r="S27" s="97" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1" s="84">
       <c r="A28" s="98" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="B28" s="98" t="inlineStr">
         <is>
-          <t>Fresh-Cut Fruit</t>
+          <t>Fresh Poultry</t>
         </is>
       </c>
       <c r="C28" s="99" t="inlineStr">
         <is>
-          <t>Pineapple &amp; Watermelon Spears</t>
+          <t>Empire Kosher Boneless Skinless Chicken Breast</t>
         </is>
       </c>
       <c r="D28" s="99" t="inlineStr">
         <is>
-          <t>Seedless Watermelon Wedge</t>
-        </is>
-      </c>
-      <c r="E28" s="99" t="n"/>
+          <t>Empire Kosher Ground Turkey</t>
+        </is>
+      </c>
+      <c r="E28" s="99" t="inlineStr">
+        <is>
+          <t>Empire Kosher Turkey Half</t>
+        </is>
+      </c>
       <c r="F28" s="99" t="n"/>
       <c r="G28" s="99" t="n"/>
       <c r="H28" s="99" t="n"/>
@@ -20673,25 +23305,36 @@
       <c r="N28" s="99" t="n"/>
       <c r="O28" s="99" t="n"/>
       <c r="P28" s="99" t="n"/>
+      <c r="Q28" s="99" t="n"/>
+      <c r="R28" s="99" t="n"/>
+      <c r="S28" s="99" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1" s="84">
       <c r="A29" s="100" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="B29" s="100" t="inlineStr">
         <is>
-          <t>Frozen Breakfast</t>
+          <t>Fresh Seafood</t>
         </is>
       </c>
       <c r="C29" s="101" t="inlineStr">
         <is>
-          <t>Van's Gluten Free Blueberry Waffles</t>
-        </is>
-      </c>
-      <c r="D29" s="101" t="n"/>
-      <c r="E29" s="101" t="n"/>
+          <t>GreenWise Keta Salmon Fillet</t>
+        </is>
+      </c>
+      <c r="D29" s="101" t="inlineStr">
+        <is>
+          <t>Salmon Fillet</t>
+        </is>
+      </c>
+      <c r="E29" s="101" t="inlineStr">
+        <is>
+          <t>Salmon Portions</t>
+        </is>
+      </c>
       <c r="F29" s="101" t="n"/>
       <c r="G29" s="101" t="n"/>
       <c r="H29" s="101" t="n"/>
@@ -20703,62 +23346,128 @@
       <c r="N29" s="101" t="n"/>
       <c r="O29" s="101" t="n"/>
       <c r="P29" s="101" t="n"/>
+      <c r="Q29" s="101" t="n"/>
+      <c r="R29" s="101" t="n"/>
+      <c r="S29" s="101" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1" s="84">
       <c r="A30" s="102" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="B30" s="102" t="inlineStr">
         <is>
-          <t>Frozen Desserts</t>
+          <t>Fresh Vegetables</t>
         </is>
       </c>
       <c r="C30" s="103" t="inlineStr">
         <is>
-          <t>Klondike Double Chocolate Bar</t>
+          <t>Baby Carrots</t>
         </is>
       </c>
       <c r="D30" s="103" t="inlineStr">
         <is>
-          <t>Yasso Greek Yogurt Bars, Coffee Chocolate Chip</t>
+          <t>Beefsteak Tomatoes</t>
         </is>
       </c>
       <c r="E30" s="103" t="inlineStr">
         <is>
-          <t>Yasso Greek Yogurt Bars, Mint Chocolate Chip</t>
-        </is>
-      </c>
-      <c r="F30" s="103" t="n"/>
-      <c r="G30" s="103" t="n"/>
-      <c r="H30" s="103" t="n"/>
-      <c r="I30" s="103" t="n"/>
-      <c r="J30" s="103" t="n"/>
-      <c r="K30" s="103" t="n"/>
-      <c r="L30" s="103" t="n"/>
-      <c r="M30" s="103" t="n"/>
-      <c r="N30" s="103" t="n"/>
-      <c r="O30" s="103" t="n"/>
-      <c r="P30" s="103" t="n"/>
+          <t>Broccoli Crowns</t>
+        </is>
+      </c>
+      <c r="F30" s="103" t="inlineStr">
+        <is>
+          <t>Fresh Trimmed Green Beans</t>
+        </is>
+      </c>
+      <c r="G30" s="103" t="inlineStr">
+        <is>
+          <t>Green Beans</t>
+        </is>
+      </c>
+      <c r="H30" s="103" t="inlineStr">
+        <is>
+          <t>Little Yellow Potatoes</t>
+        </is>
+      </c>
+      <c r="I30" s="103" t="inlineStr">
+        <is>
+          <t>Medley Potatoes</t>
+        </is>
+      </c>
+      <c r="J30" s="103" t="inlineStr">
+        <is>
+          <t>Mini Cucumbers</t>
+        </is>
+      </c>
+      <c r="K30" s="103" t="inlineStr">
+        <is>
+          <t>Multi-Color Peppers, 3-Pack</t>
+        </is>
+      </c>
+      <c r="L30" s="103" t="inlineStr">
+        <is>
+          <t>Organic Celery Hearts</t>
+        </is>
+      </c>
+      <c r="M30" s="103" t="inlineStr">
+        <is>
+          <t>Organic Kale</t>
+        </is>
+      </c>
+      <c r="N30" s="103" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="O30" s="103" t="inlineStr">
+        <is>
+          <t>Red Onions</t>
+        </is>
+      </c>
+      <c r="P30" s="103" t="inlineStr">
+        <is>
+          <t>Ruby Sensation Potato Nibbles</t>
+        </is>
+      </c>
+      <c r="Q30" s="103" t="inlineStr">
+        <is>
+          <t>Tomatoes on the Vine</t>
+        </is>
+      </c>
+      <c r="R30" s="103" t="inlineStr">
+        <is>
+          <t>Yellow Squash</t>
+        </is>
+      </c>
+      <c r="S30" s="103" t="inlineStr">
+        <is>
+          <t>Zucchini</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="36" customHeight="1" s="84">
       <c r="A31" s="104" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="B31" s="104" t="inlineStr">
         <is>
-          <t>Frozen Meat</t>
+          <t>Fresh-Cut Fruit</t>
         </is>
       </c>
       <c r="C31" s="105" t="inlineStr">
         <is>
-          <t>Applegate Chicken &amp; Maple Breakfast Sausage</t>
-        </is>
-      </c>
-      <c r="D31" s="105" t="n"/>
+          <t>Pineapple &amp; Watermelon Spears</t>
+        </is>
+      </c>
+      <c r="D31" s="105" t="inlineStr">
+        <is>
+          <t>Seedless Watermelon Wedge</t>
+        </is>
+      </c>
       <c r="E31" s="105" t="n"/>
       <c r="F31" s="105" t="n"/>
       <c r="G31" s="105" t="n"/>
@@ -20771,6 +23480,9 @@
       <c r="N31" s="105" t="n"/>
       <c r="O31" s="105" t="n"/>
       <c r="P31" s="105" t="n"/>
+      <c r="Q31" s="105" t="n"/>
+      <c r="R31" s="105" t="n"/>
+      <c r="S31" s="105" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1" s="84">
       <c r="A32" s="94" t="inlineStr">
@@ -20780,12 +23492,12 @@
       </c>
       <c r="B32" s="94" t="inlineStr">
         <is>
-          <t>Frozen Pizza</t>
+          <t>Frozen Appetizers</t>
         </is>
       </c>
       <c r="C32" s="95" t="inlineStr">
         <is>
-          <t>Cauliflower Crust Pizza</t>
+          <t>Black Bean &amp; Cheese Taquitos</t>
         </is>
       </c>
       <c r="D32" s="95" t="n"/>
@@ -20801,21 +23513,24 @@
       <c r="N32" s="95" t="n"/>
       <c r="O32" s="95" t="n"/>
       <c r="P32" s="95" t="n"/>
+      <c r="Q32" s="95" t="n"/>
+      <c r="R32" s="95" t="n"/>
+      <c r="S32" s="95" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1" s="84">
       <c r="A33" s="96" t="inlineStr">
         <is>
-          <t>Frozen Food</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="B33" s="96" t="inlineStr">
         <is>
-          <t>Frozen Vegetables</t>
+          <t>Frozen Breakfast</t>
         </is>
       </c>
       <c r="C33" s="97" t="inlineStr">
         <is>
-          <t>Birds Eye Steamfresh Sweet Peas</t>
+          <t>Van's Gluten Free Blueberry Waffles</t>
         </is>
       </c>
       <c r="D33" s="97" t="n"/>
@@ -20831,25 +23546,36 @@
       <c r="N33" s="97" t="n"/>
       <c r="O33" s="97" t="n"/>
       <c r="P33" s="97" t="n"/>
+      <c r="Q33" s="97" t="n"/>
+      <c r="R33" s="97" t="n"/>
+      <c r="S33" s="97" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1" s="84">
       <c r="A34" s="98" t="inlineStr">
         <is>
-          <t>Self Care</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="B34" s="98" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Frozen Desserts</t>
         </is>
       </c>
       <c r="C34" s="99" t="inlineStr">
         <is>
-          <t>Honest Company Conditioning Detangler</t>
-        </is>
-      </c>
-      <c r="D34" s="99" t="n"/>
-      <c r="E34" s="99" t="n"/>
+          <t>Klondike Double Chocolate Bar</t>
+        </is>
+      </c>
+      <c r="D34" s="99" t="inlineStr">
+        <is>
+          <t>Yasso Greek Yogurt Bars, Coffee Chocolate Chip</t>
+        </is>
+      </c>
+      <c r="E34" s="99" t="inlineStr">
+        <is>
+          <t>Yasso Greek Yogurt Bars, Mint Chocolate Chip</t>
+        </is>
+      </c>
       <c r="F34" s="99" t="n"/>
       <c r="G34" s="99" t="n"/>
       <c r="H34" s="99" t="n"/>
@@ -20861,21 +23587,24 @@
       <c r="N34" s="99" t="n"/>
       <c r="O34" s="99" t="n"/>
       <c r="P34" s="99" t="n"/>
+      <c r="Q34" s="99" t="n"/>
+      <c r="R34" s="99" t="n"/>
+      <c r="S34" s="99" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1" s="84">
       <c r="A35" s="100" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="B35" s="100" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Frozen Meat</t>
         </is>
       </c>
       <c r="C35" s="101" t="inlineStr">
         <is>
-          <t>Command Heavy Duty Picture Hangers</t>
+          <t>Applegate Chicken &amp; Maple Breakfast Sausage</t>
         </is>
       </c>
       <c r="D35" s="101" t="n"/>
@@ -20891,21 +23620,24 @@
       <c r="N35" s="101" t="n"/>
       <c r="O35" s="101" t="n"/>
       <c r="P35" s="101" t="n"/>
+      <c r="Q35" s="101" t="n"/>
+      <c r="R35" s="101" t="n"/>
+      <c r="S35" s="101" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1" s="84">
       <c r="A36" s="102" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Frozen Food</t>
         </is>
       </c>
       <c r="B36" s="102" t="inlineStr">
         <is>
-          <t>Hot Dogs &amp; Sausages</t>
+          <t>Frozen Pizza</t>
         </is>
       </c>
       <c r="C36" s="103" t="inlineStr">
         <is>
-          <t>Hebrew National Beef Franks</t>
+          <t>Cauliflower Crust Pizza</t>
         </is>
       </c>
       <c r="D36" s="103" t="n"/>
@@ -20921,21 +23653,24 @@
       <c r="N36" s="103" t="n"/>
       <c r="O36" s="103" t="n"/>
       <c r="P36" s="103" t="n"/>
+      <c r="Q36" s="103" t="n"/>
+      <c r="R36" s="103" t="n"/>
+      <c r="S36" s="103" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1" s="84">
       <c r="A37" s="104" t="inlineStr">
         <is>
-          <t>Toiletries, Cleaning and Disposables</t>
+          <t>Frozen Food</t>
         </is>
       </c>
       <c r="B37" s="104" t="inlineStr">
         <is>
-          <t>Household Cleaners</t>
+          <t>Frozen Vegetables</t>
         </is>
       </c>
       <c r="C37" s="105" t="inlineStr">
         <is>
-          <t>Weiman Granite &amp; Stone Cleaner &amp; Polish</t>
+          <t>Birds Eye Steamfresh Sweet Peas</t>
         </is>
       </c>
       <c r="D37" s="105" t="n"/>
@@ -20951,24 +23686,31 @@
       <c r="N37" s="105" t="n"/>
       <c r="O37" s="105" t="n"/>
       <c r="P37" s="105" t="n"/>
+      <c r="Q37" s="105" t="n"/>
+      <c r="R37" s="105" t="n"/>
+      <c r="S37" s="105" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1" s="84">
       <c r="A38" s="94" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Self Care</t>
         </is>
       </c>
       <c r="B38" s="94" t="inlineStr">
         <is>
-          <t>Jarred Vegetables</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="C38" s="95" t="inlineStr">
         <is>
-          <t>Fire Roasted Red Peppers</t>
-        </is>
-      </c>
-      <c r="D38" s="95" t="n"/>
+          <t>Head &amp; Shoulders</t>
+        </is>
+      </c>
+      <c r="D38" s="95" t="inlineStr">
+        <is>
+          <t>Honest Company Conditioning Detangler</t>
+        </is>
+      </c>
       <c r="E38" s="95" t="n"/>
       <c r="F38" s="95" t="n"/>
       <c r="G38" s="95" t="n"/>
@@ -20981,21 +23723,24 @@
       <c r="N38" s="95" t="n"/>
       <c r="O38" s="95" t="n"/>
       <c r="P38" s="95" t="n"/>
+      <c r="Q38" s="95" t="n"/>
+      <c r="R38" s="95" t="n"/>
+      <c r="S38" s="95" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1" s="84">
       <c r="A39" s="96" t="inlineStr">
         <is>
-          <t>Torah</t>
+          <t>Home Improvement</t>
         </is>
       </c>
       <c r="B39" s="96" t="inlineStr">
         <is>
-          <t>Judaica</t>
+          <t>Home Improvement</t>
         </is>
       </c>
       <c r="C39" s="97" t="inlineStr">
         <is>
-          <t>Yehuda Sabbath Candles</t>
+          <t>Command Heavy Duty Picture Hangers</t>
         </is>
       </c>
       <c r="D39" s="97" t="n"/>
@@ -21011,28 +23756,27 @@
       <c r="N39" s="97" t="n"/>
       <c r="O39" s="97" t="n"/>
       <c r="P39" s="97" t="n"/>
+      <c r="Q39" s="97" t="n"/>
+      <c r="R39" s="97" t="n"/>
+      <c r="S39" s="97" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1" s="84">
       <c r="A40" s="98" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="B40" s="98" t="inlineStr">
         <is>
-          <t>Macaroni &amp; Cheese</t>
+          <t>Hot Dogs &amp; Sausages</t>
         </is>
       </c>
       <c r="C40" s="99" t="inlineStr">
         <is>
-          <t>Annie's Gluten-Free Deluxe Shells &amp; Cheddar</t>
-        </is>
-      </c>
-      <c r="D40" s="99" t="inlineStr">
-        <is>
-          <t>Banza White Cheddar Shells</t>
-        </is>
-      </c>
+          <t>Hebrew National Beef Franks</t>
+        </is>
+      </c>
+      <c r="D40" s="99" t="n"/>
       <c r="E40" s="99" t="n"/>
       <c r="F40" s="99" t="n"/>
       <c r="G40" s="99" t="n"/>
@@ -21045,21 +23789,24 @@
       <c r="N40" s="99" t="n"/>
       <c r="O40" s="99" t="n"/>
       <c r="P40" s="99" t="n"/>
+      <c r="Q40" s="99" t="n"/>
+      <c r="R40" s="99" t="n"/>
+      <c r="S40" s="99" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1" s="84">
       <c r="A41" s="100" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Toiletries, Cleaning and Disposables</t>
         </is>
       </c>
       <c r="B41" s="100" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Household Cleaners</t>
         </is>
       </c>
       <c r="C41" s="101" t="inlineStr">
         <is>
-          <t>Fairlife Chocolate Milk</t>
+          <t>Weiman Granite &amp; Stone Cleaner &amp; Polish</t>
         </is>
       </c>
       <c r="D41" s="101" t="n"/>
@@ -21075,21 +23822,24 @@
       <c r="N41" s="101" t="n"/>
       <c r="O41" s="101" t="n"/>
       <c r="P41" s="101" t="n"/>
+      <c r="Q41" s="101" t="n"/>
+      <c r="R41" s="101" t="n"/>
+      <c r="S41" s="101" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1" s="84">
       <c r="A42" s="102" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="B42" s="102" t="inlineStr">
         <is>
-          <t>Muffins &amp; Pastries</t>
+          <t>Jarred Vegetables</t>
         </is>
       </c>
       <c r="C42" s="103" t="inlineStr">
         <is>
-          <t>Gluten-Free Blueberry Muffins</t>
+          <t>Fire Roasted Red Peppers</t>
         </is>
       </c>
       <c r="D42" s="103" t="n"/>
@@ -21105,21 +23855,24 @@
       <c r="N42" s="103" t="n"/>
       <c r="O42" s="103" t="n"/>
       <c r="P42" s="103" t="n"/>
+      <c r="Q42" s="103" t="n"/>
+      <c r="R42" s="103" t="n"/>
+      <c r="S42" s="103" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1" s="84">
       <c r="A43" s="104" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Torah</t>
         </is>
       </c>
       <c r="B43" s="104" t="inlineStr">
         <is>
-          <t>Pasta</t>
+          <t>Judaica</t>
         </is>
       </c>
       <c r="C43" s="105" t="inlineStr">
         <is>
-          <t>Chickpea Fusilli Pasta</t>
+          <t>Yehuda Sabbath Candles</t>
         </is>
       </c>
       <c r="D43" s="105" t="n"/>
@@ -21135,6 +23888,9 @@
       <c r="N43" s="105" t="n"/>
       <c r="O43" s="105" t="n"/>
       <c r="P43" s="105" t="n"/>
+      <c r="Q43" s="105" t="n"/>
+      <c r="R43" s="105" t="n"/>
+      <c r="S43" s="105" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1" s="84">
       <c r="A44" s="94" t="inlineStr">
@@ -21144,15 +23900,19 @@
       </c>
       <c r="B44" s="94" t="inlineStr">
         <is>
-          <t>Peanut Butter</t>
+          <t>Macaroni &amp; Cheese</t>
         </is>
       </c>
       <c r="C44" s="95" t="inlineStr">
         <is>
-          <t>Jif No Sugar Added Creamy Peanut Butter</t>
-        </is>
-      </c>
-      <c r="D44" s="95" t="n"/>
+          <t>Annie's Gluten-Free Deluxe Shells &amp; Cheddar</t>
+        </is>
+      </c>
+      <c r="D44" s="95" t="inlineStr">
+        <is>
+          <t>Banza White Cheddar Shells</t>
+        </is>
+      </c>
       <c r="E44" s="95" t="n"/>
       <c r="F44" s="95" t="n"/>
       <c r="G44" s="95" t="n"/>
@@ -21165,6 +23925,9 @@
       <c r="N44" s="95" t="n"/>
       <c r="O44" s="95" t="n"/>
       <c r="P44" s="95" t="n"/>
+      <c r="Q44" s="95" t="n"/>
+      <c r="R44" s="95" t="n"/>
+      <c r="S44" s="95" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1" s="84">
       <c r="A45" s="96" t="inlineStr">
@@ -21174,12 +23937,12 @@
       </c>
       <c r="B45" s="96" t="inlineStr">
         <is>
-          <t>Plant-Based Cheese</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="C45" s="97" t="inlineStr">
         <is>
-          <t>Daiya Mexican Blend Shreds</t>
+          <t>Fairlife Chocolate Milk</t>
         </is>
       </c>
       <c r="D45" s="97" t="n"/>
@@ -21195,26 +23958,29 @@
       <c r="N45" s="97" t="n"/>
       <c r="O45" s="97" t="n"/>
       <c r="P45" s="97" t="n"/>
+      <c r="Q45" s="97" t="n"/>
+      <c r="R45" s="97" t="n"/>
+      <c r="S45" s="97" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1" s="84">
       <c r="A46" s="98" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="B46" s="98" t="inlineStr">
         <is>
-          <t>Plant-Based Milk</t>
+          <t>Muffins &amp; Pastries</t>
         </is>
       </c>
       <c r="C46" s="99" t="inlineStr">
         <is>
-          <t>Chobani Extra Creamy Oatmilk</t>
+          <t>Chocolate Babka</t>
         </is>
       </c>
       <c r="D46" s="99" t="inlineStr">
         <is>
-          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
+          <t>Gluten-Free Blueberry Muffins</t>
         </is>
       </c>
       <c r="E46" s="99" t="n"/>
@@ -21229,21 +23995,24 @@
       <c r="N46" s="99" t="n"/>
       <c r="O46" s="99" t="n"/>
       <c r="P46" s="99" t="n"/>
+      <c r="Q46" s="99" t="n"/>
+      <c r="R46" s="99" t="n"/>
+      <c r="S46" s="99" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1" s="84">
       <c r="A47" s="100" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Toiletries, Cleaning and Disposables</t>
         </is>
       </c>
       <c r="B47" s="100" t="inlineStr">
         <is>
-          <t>Popcorn</t>
+          <t>Paper Towels</t>
         </is>
       </c>
       <c r="C47" s="101" t="inlineStr">
         <is>
-          <t>LesserEvil Popcorn</t>
+          <t>Paper Towels, 2-Roll</t>
         </is>
       </c>
       <c r="D47" s="101" t="n"/>
@@ -21259,28 +24028,27 @@
       <c r="N47" s="101" t="n"/>
       <c r="O47" s="101" t="n"/>
       <c r="P47" s="101" t="n"/>
+      <c r="Q47" s="101" t="n"/>
+      <c r="R47" s="101" t="n"/>
+      <c r="S47" s="101" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1" s="84">
       <c r="A48" s="102" t="inlineStr">
         <is>
-          <t>Prepared Eating</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="B48" s="102" t="inlineStr">
         <is>
-          <t>Prepared Coffee</t>
+          <t>Pasta</t>
         </is>
       </c>
       <c r="C48" s="103" t="inlineStr">
         <is>
-          <t>1 Caramel Macchiato</t>
-        </is>
-      </c>
-      <c r="D48" s="103" t="inlineStr">
-        <is>
-          <t>1 Iced Caramel Macchiato</t>
-        </is>
-      </c>
+          <t>Chickpea Fusilli Pasta</t>
+        </is>
+      </c>
+      <c r="D48" s="103" t="n"/>
       <c r="E48" s="103" t="n"/>
       <c r="F48" s="103" t="n"/>
       <c r="G48" s="103" t="n"/>
@@ -21293,28 +24061,27 @@
       <c r="N48" s="103" t="n"/>
       <c r="O48" s="103" t="n"/>
       <c r="P48" s="103" t="n"/>
+      <c r="Q48" s="103" t="n"/>
+      <c r="R48" s="103" t="n"/>
+      <c r="S48" s="103" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1" s="84">
       <c r="A49" s="104" t="inlineStr">
         <is>
-          <t>Prepared Eating</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="B49" s="104" t="inlineStr">
         <is>
-          <t>Prepared Meals</t>
+          <t>Peanut Butter</t>
         </is>
       </c>
       <c r="C49" s="105" t="inlineStr">
         <is>
-          <t>1 Chicken N French Toast</t>
-        </is>
-      </c>
-      <c r="D49" s="105" t="inlineStr">
-        <is>
-          <t>1 Frenchy Plate</t>
-        </is>
-      </c>
+          <t>Jif No Sugar Added Creamy Peanut Butter</t>
+        </is>
+      </c>
+      <c r="D49" s="105" t="n"/>
       <c r="E49" s="105" t="n"/>
       <c r="F49" s="105" t="n"/>
       <c r="G49" s="105" t="n"/>
@@ -21327,21 +24094,24 @@
       <c r="N49" s="105" t="n"/>
       <c r="O49" s="105" t="n"/>
       <c r="P49" s="105" t="n"/>
+      <c r="Q49" s="105" t="n"/>
+      <c r="R49" s="105" t="n"/>
+      <c r="S49" s="105" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1" s="84">
       <c r="A50" s="94" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B50" s="94" t="inlineStr">
         <is>
-          <t>Refrigerated Dough</t>
+          <t>Plant-Based Cheese</t>
         </is>
       </c>
       <c r="C50" s="95" t="inlineStr">
         <is>
-          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
+          <t>Daiya Mexican Blend Shreds</t>
         </is>
       </c>
       <c r="D50" s="95" t="n"/>
@@ -21357,24 +24127,31 @@
       <c r="N50" s="95" t="n"/>
       <c r="O50" s="95" t="n"/>
       <c r="P50" s="95" t="n"/>
+      <c r="Q50" s="95" t="n"/>
+      <c r="R50" s="95" t="n"/>
+      <c r="S50" s="95" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1" s="84">
       <c r="A51" s="96" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="B51" s="96" t="inlineStr">
         <is>
-          <t>Rice &amp; Grains</t>
+          <t>Plant-Based Milk</t>
         </is>
       </c>
       <c r="C51" s="97" t="inlineStr">
         <is>
-          <t>Mahatma Jasmine Rice</t>
-        </is>
-      </c>
-      <c r="D51" s="97" t="n"/>
+          <t>Chobani Extra Creamy Oatmilk</t>
+        </is>
+      </c>
+      <c r="D51" s="97" t="inlineStr">
+        <is>
+          <t>Silk Organic Unsweet Soymilk, Half Gallon</t>
+        </is>
+      </c>
       <c r="E51" s="97" t="n"/>
       <c r="F51" s="97" t="n"/>
       <c r="G51" s="97" t="n"/>
@@ -21387,6 +24164,9 @@
       <c r="N51" s="97" t="n"/>
       <c r="O51" s="97" t="n"/>
       <c r="P51" s="97" t="n"/>
+      <c r="Q51" s="97" t="n"/>
+      <c r="R51" s="97" t="n"/>
+      <c r="S51" s="97" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1" s="84">
       <c r="A52" s="98" t="inlineStr">
@@ -21396,19 +24176,15 @@
       </c>
       <c r="B52" s="98" t="inlineStr">
         <is>
-          <t>Rice Cakes &amp; Crisps</t>
+          <t>Popcorn</t>
         </is>
       </c>
       <c r="C52" s="99" t="inlineStr">
         <is>
-          <t>Quaker Rice Crisps Apple Cinnamon</t>
-        </is>
-      </c>
-      <c r="D52" s="99" t="inlineStr">
-        <is>
-          <t>Quaker Rice Crisps Chocolate</t>
-        </is>
-      </c>
+          <t>LesserEvil Popcorn</t>
+        </is>
+      </c>
+      <c r="D52" s="99" t="n"/>
       <c r="E52" s="99" t="n"/>
       <c r="F52" s="99" t="n"/>
       <c r="G52" s="99" t="n"/>
@@ -21421,24 +24197,31 @@
       <c r="N52" s="99" t="n"/>
       <c r="O52" s="99" t="n"/>
       <c r="P52" s="99" t="n"/>
+      <c r="Q52" s="99" t="n"/>
+      <c r="R52" s="99" t="n"/>
+      <c r="S52" s="99" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1" s="84">
       <c r="A53" s="100" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>Prepared Eating</t>
         </is>
       </c>
       <c r="B53" s="100" t="inlineStr">
         <is>
-          <t>Salad Dressing</t>
+          <t>Prepared Coffee</t>
         </is>
       </c>
       <c r="C53" s="101" t="inlineStr">
         <is>
-          <t>Vinaigrette Dressing</t>
-        </is>
-      </c>
-      <c r="D53" s="101" t="n"/>
+          <t>1 Caramel Macchiato</t>
+        </is>
+      </c>
+      <c r="D53" s="101" t="inlineStr">
+        <is>
+          <t>1 Iced Caramel Macchiato</t>
+        </is>
+      </c>
       <c r="E53" s="101" t="n"/>
       <c r="F53" s="101" t="n"/>
       <c r="G53" s="101" t="n"/>
@@ -21451,38 +24234,33 @@
       <c r="N53" s="101" t="n"/>
       <c r="O53" s="101" t="n"/>
       <c r="P53" s="101" t="n"/>
+      <c r="Q53" s="101" t="n"/>
+      <c r="R53" s="101" t="n"/>
+      <c r="S53" s="101" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1" s="84">
       <c r="A54" s="102" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Prepared Eating</t>
         </is>
       </c>
       <c r="B54" s="102" t="inlineStr">
         <is>
-          <t>Salad Kits</t>
+          <t>Prepared Meals</t>
         </is>
       </c>
       <c r="C54" s="103" t="inlineStr">
         <is>
-          <t>Publix Makoto Ginger Salad</t>
+          <t>1 Chicken N French Toast</t>
         </is>
       </c>
       <c r="D54" s="103" t="inlineStr">
         <is>
-          <t>Publix True Bleu Salad Kit</t>
-        </is>
-      </c>
-      <c r="E54" s="103" t="inlineStr">
-        <is>
-          <t>Taylor Farms Chopped Caesar Salad Kit</t>
-        </is>
-      </c>
-      <c r="F54" s="103" t="inlineStr">
-        <is>
-          <t>Taylor Farms Everything Chopped Salad Kit</t>
-        </is>
-      </c>
+          <t>1 Frenchy Plate</t>
+        </is>
+      </c>
+      <c r="E54" s="103" t="n"/>
+      <c r="F54" s="103" t="n"/>
       <c r="G54" s="103" t="n"/>
       <c r="H54" s="103" t="n"/>
       <c r="I54" s="103" t="n"/>
@@ -21493,24 +24271,31 @@
       <c r="N54" s="103" t="n"/>
       <c r="O54" s="103" t="n"/>
       <c r="P54" s="103" t="n"/>
+      <c r="Q54" s="103" t="n"/>
+      <c r="R54" s="103" t="n"/>
+      <c r="S54" s="103" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1" s="84">
       <c r="A55" s="104" t="inlineStr">
         <is>
-          <t>Condiments &amp; Seasonings</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="B55" s="104" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Refrigerated Dough</t>
         </is>
       </c>
       <c r="C55" s="105" t="inlineStr">
         <is>
-          <t>Cholula Cremosa Cilantro Lime Sauce</t>
-        </is>
-      </c>
-      <c r="D55" s="105" t="n"/>
+          <t>Pillsbury Flaky Biscuits</t>
+        </is>
+      </c>
+      <c r="D55" s="105" t="inlineStr">
+        <is>
+          <t>Sweet Loren's Gluten Free Brownie Cookie Dough</t>
+        </is>
+      </c>
       <c r="E55" s="105" t="n"/>
       <c r="F55" s="105" t="n"/>
       <c r="G55" s="105" t="n"/>
@@ -21523,33 +24308,28 @@
       <c r="N55" s="105" t="n"/>
       <c r="O55" s="105" t="n"/>
       <c r="P55" s="105" t="n"/>
+      <c r="Q55" s="105" t="n"/>
+      <c r="R55" s="105" t="n"/>
+      <c r="S55" s="105" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1" s="84">
       <c r="A56" s="94" t="inlineStr">
         <is>
-          <t>Condiments &amp; Seasonings</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="B56" s="94" t="inlineStr">
         <is>
-          <t>Seasonings &amp; Spices</t>
+          <t>Rice &amp; Grains</t>
         </is>
       </c>
       <c r="C56" s="95" t="inlineStr">
         <is>
-          <t>Lawry's Garlic Salt</t>
-        </is>
-      </c>
-      <c r="D56" s="95" t="inlineStr">
-        <is>
-          <t>McCormick Everything Bagel Seasoning</t>
-        </is>
-      </c>
-      <c r="E56" s="95" t="inlineStr">
-        <is>
-          <t>McCormick Sea Salt Grinder</t>
-        </is>
-      </c>
+          <t>Mahatma Jasmine Rice</t>
+        </is>
+      </c>
+      <c r="D56" s="95" t="n"/>
+      <c r="E56" s="95" t="n"/>
       <c r="F56" s="95" t="n"/>
       <c r="G56" s="95" t="n"/>
       <c r="H56" s="95" t="n"/>
@@ -21561,24 +24341,31 @@
       <c r="N56" s="95" t="n"/>
       <c r="O56" s="95" t="n"/>
       <c r="P56" s="95" t="n"/>
+      <c r="Q56" s="95" t="n"/>
+      <c r="R56" s="95" t="n"/>
+      <c r="S56" s="95" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1" s="84">
       <c r="A57" s="96" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="B57" s="96" t="inlineStr">
         <is>
-          <t>Smoked Seafood</t>
+          <t>Rice Cakes &amp; Crisps</t>
         </is>
       </c>
       <c r="C57" s="97" t="inlineStr">
         <is>
-          <t>Smoked Salmon with Pepper</t>
-        </is>
-      </c>
-      <c r="D57" s="97" t="n"/>
+          <t>Quaker Rice Crisps Apple Cinnamon</t>
+        </is>
+      </c>
+      <c r="D57" s="97" t="inlineStr">
+        <is>
+          <t>Quaker Rice Crisps Chocolate</t>
+        </is>
+      </c>
       <c r="E57" s="97" t="n"/>
       <c r="F57" s="97" t="n"/>
       <c r="G57" s="97" t="n"/>
@@ -21591,6 +24378,9 @@
       <c r="N57" s="97" t="n"/>
       <c r="O57" s="97" t="n"/>
       <c r="P57" s="97" t="n"/>
+      <c r="Q57" s="97" t="n"/>
+      <c r="R57" s="97" t="n"/>
+      <c r="S57" s="97" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1" s="84">
       <c r="A58" s="98" t="inlineStr">
@@ -21600,19 +24390,15 @@
       </c>
       <c r="B58" s="98" t="inlineStr">
         <is>
-          <t>Snack Bars</t>
+          <t>Salad Dressing</t>
         </is>
       </c>
       <c r="C58" s="99" t="inlineStr">
         <is>
-          <t>Fruit &amp; Grain Bars</t>
-        </is>
-      </c>
-      <c r="D58" s="99" t="inlineStr">
-        <is>
-          <t>Nature's Bakery Gluten-Free Raspberry Fig Bars</t>
-        </is>
-      </c>
+          <t>Vinaigrette Dressing</t>
+        </is>
+      </c>
+      <c r="D58" s="99" t="n"/>
       <c r="E58" s="99" t="n"/>
       <c r="F58" s="99" t="n"/>
       <c r="G58" s="99" t="n"/>
@@ -21625,27 +24411,46 @@
       <c r="N58" s="99" t="n"/>
       <c r="O58" s="99" t="n"/>
       <c r="P58" s="99" t="n"/>
+      <c r="Q58" s="99" t="n"/>
+      <c r="R58" s="99" t="n"/>
+      <c r="S58" s="99" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1" s="84">
       <c r="A59" s="100" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="B59" s="100" t="inlineStr">
         <is>
-          <t>Snack Cakes</t>
+          <t>Salad Kits</t>
         </is>
       </c>
       <c r="C59" s="101" t="inlineStr">
         <is>
-          <t>Little Debbie Cosmic Brownies</t>
-        </is>
-      </c>
-      <c r="D59" s="101" t="n"/>
-      <c r="E59" s="101" t="n"/>
-      <c r="F59" s="101" t="n"/>
-      <c r="G59" s="101" t="n"/>
+          <t>Complete Sweet Kale Salad Kit</t>
+        </is>
+      </c>
+      <c r="D59" s="101" t="inlineStr">
+        <is>
+          <t>Publix Makoto Ginger Salad</t>
+        </is>
+      </c>
+      <c r="E59" s="101" t="inlineStr">
+        <is>
+          <t>Publix True Bleu Salad Kit</t>
+        </is>
+      </c>
+      <c r="F59" s="101" t="inlineStr">
+        <is>
+          <t>Taylor Farms Chopped Caesar Salad Kit</t>
+        </is>
+      </c>
+      <c r="G59" s="101" t="inlineStr">
+        <is>
+          <t>Taylor Farms Everything Chopped Salad Kit</t>
+        </is>
+      </c>
       <c r="H59" s="101" t="n"/>
       <c r="I59" s="101" t="n"/>
       <c r="J59" s="101" t="n"/>
@@ -21655,28 +24460,27 @@
       <c r="N59" s="101" t="n"/>
       <c r="O59" s="101" t="n"/>
       <c r="P59" s="101" t="n"/>
+      <c r="Q59" s="101" t="n"/>
+      <c r="R59" s="101" t="n"/>
+      <c r="S59" s="101" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1" s="84">
       <c r="A60" s="102" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Condiments &amp; Seasonings</t>
         </is>
       </c>
       <c r="B60" s="102" t="inlineStr">
         <is>
-          <t>Specialty Cheese</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C60" s="103" t="inlineStr">
         <is>
-          <t>Feta Cheese Crumbles</t>
-        </is>
-      </c>
-      <c r="D60" s="103" t="inlineStr">
-        <is>
-          <t>Goat Cheese Logs</t>
-        </is>
-      </c>
+          <t>Cholula Cremosa Cilantro Lime Sauce</t>
+        </is>
+      </c>
+      <c r="D60" s="103" t="n"/>
       <c r="E60" s="103" t="n"/>
       <c r="F60" s="103" t="n"/>
       <c r="G60" s="103" t="n"/>
@@ -21689,27 +24493,46 @@
       <c r="N60" s="103" t="n"/>
       <c r="O60" s="103" t="n"/>
       <c r="P60" s="103" t="n"/>
+      <c r="Q60" s="103" t="n"/>
+      <c r="R60" s="103" t="n"/>
+      <c r="S60" s="103" t="n"/>
     </row>
     <row r="61" ht="36" customHeight="1" s="84">
       <c r="A61" s="104" t="inlineStr">
         <is>
-          <t>Toiletries, Cleaning and Disposables</t>
+          <t>Condiments &amp; Seasonings</t>
         </is>
       </c>
       <c r="B61" s="104" t="inlineStr">
         <is>
-          <t>Storage &amp; Organization</t>
+          <t>Seasonings &amp; Spices</t>
         </is>
       </c>
       <c r="C61" s="105" t="inlineStr">
         <is>
-          <t>Collapsible Storage Container/Bin</t>
-        </is>
-      </c>
-      <c r="D61" s="105" t="n"/>
-      <c r="E61" s="105" t="n"/>
-      <c r="F61" s="105" t="n"/>
-      <c r="G61" s="105" t="n"/>
+          <t>Lawry's Garlic Salt</t>
+        </is>
+      </c>
+      <c r="D61" s="105" t="inlineStr">
+        <is>
+          <t>McCormick Everything Bagel Seasoning</t>
+        </is>
+      </c>
+      <c r="E61" s="105" t="inlineStr">
+        <is>
+          <t>McCormick Sea Salt Grinder</t>
+        </is>
+      </c>
+      <c r="F61" s="105" t="inlineStr">
+        <is>
+          <t>Peppercorn Grinder</t>
+        </is>
+      </c>
+      <c r="G61" s="105" t="inlineStr">
+        <is>
+          <t>Salt Grinder</t>
+        </is>
+      </c>
       <c r="H61" s="105" t="n"/>
       <c r="I61" s="105" t="n"/>
       <c r="J61" s="105" t="n"/>
@@ -21719,28 +24542,27 @@
       <c r="N61" s="105" t="n"/>
       <c r="O61" s="105" t="n"/>
       <c r="P61" s="105" t="n"/>
+      <c r="Q61" s="105" t="n"/>
+      <c r="R61" s="105" t="n"/>
+      <c r="S61" s="105" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1" s="84">
       <c r="A62" s="94" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="B62" s="94" t="inlineStr">
         <is>
-          <t>Wine</t>
+          <t>Smoked Seafood</t>
         </is>
       </c>
       <c r="C62" s="95" t="inlineStr">
         <is>
-          <t>Häagen-Dazs Blackberry Ice Cream</t>
-        </is>
-      </c>
-      <c r="D62" s="95" t="inlineStr">
-        <is>
-          <t>Magen David Blackberry Wine</t>
-        </is>
-      </c>
+          <t>Smoked Salmon with Pepper</t>
+        </is>
+      </c>
+      <c r="D62" s="95" t="n"/>
       <c r="E62" s="95" t="n"/>
       <c r="F62" s="95" t="n"/>
       <c r="G62" s="95" t="n"/>
@@ -21753,24 +24575,31 @@
       <c r="N62" s="95" t="n"/>
       <c r="O62" s="95" t="n"/>
       <c r="P62" s="95" t="n"/>
+      <c r="Q62" s="95" t="n"/>
+      <c r="R62" s="95" t="n"/>
+      <c r="S62" s="95" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1" s="84">
       <c r="A63" s="96" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Pantry</t>
         </is>
       </c>
       <c r="B63" s="96" t="inlineStr">
         <is>
-          <t>Writing Supplies</t>
+          <t>Snack Bars</t>
         </is>
       </c>
       <c r="C63" s="97" t="inlineStr">
         <is>
-          <t>Gel Pens, 3-Pack</t>
-        </is>
-      </c>
-      <c r="D63" s="97" t="n"/>
+          <t>Fruit &amp; Grain Bars</t>
+        </is>
+      </c>
+      <c r="D63" s="97" t="inlineStr">
+        <is>
+          <t>Nature's Bakery Gluten-Free Raspberry Fig Bars</t>
+        </is>
+      </c>
       <c r="E63" s="97" t="n"/>
       <c r="F63" s="97" t="n"/>
       <c r="G63" s="97" t="n"/>
@@ -21783,43 +24612,30 @@
       <c r="N63" s="97" t="n"/>
       <c r="O63" s="97" t="n"/>
       <c r="P63" s="97" t="n"/>
+      <c r="Q63" s="97" t="n"/>
+      <c r="R63" s="97" t="n"/>
+      <c r="S63" s="97" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1" s="84">
       <c r="A64" s="98" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Dessert</t>
         </is>
       </c>
       <c r="B64" s="98" t="inlineStr">
         <is>
-          <t>Yogurt</t>
+          <t>Snack Cakes</t>
         </is>
       </c>
       <c r="C64" s="99" t="inlineStr">
         <is>
-          <t>Chobani Greek Yogurt 4-Pack, Hero Batch</t>
-        </is>
-      </c>
-      <c r="D64" s="99" t="inlineStr">
-        <is>
-          <t>Chobani Protein Greek Yogurt Drink, Strawberries &amp; Cream</t>
-        </is>
-      </c>
-      <c r="E64" s="99" t="inlineStr">
-        <is>
-          <t>Chobani Vanilla Mixed Berry Greek Yogurt</t>
-        </is>
-      </c>
-      <c r="F64" s="99" t="inlineStr">
-        <is>
-          <t>Stonyfield Organic YoBaby Yogurt Pouch, Banana</t>
-        </is>
-      </c>
-      <c r="G64" s="99" t="inlineStr">
-        <is>
-          <t>Stonyfield Organic YoBaby Yogurt Pouch, Peach</t>
-        </is>
-      </c>
+          <t>Little Debbie Cosmic Brownies</t>
+        </is>
+      </c>
+      <c r="D64" s="99" t="n"/>
+      <c r="E64" s="99" t="n"/>
+      <c r="F64" s="99" t="n"/>
+      <c r="G64" s="99" t="n"/>
       <c r="H64" s="99" t="n"/>
       <c r="I64" s="99" t="n"/>
       <c r="J64" s="99" t="n"/>
@@ -21829,9 +24645,201 @@
       <c r="N64" s="99" t="n"/>
       <c r="O64" s="99" t="n"/>
       <c r="P64" s="99" t="n"/>
+      <c r="Q64" s="99" t="n"/>
+      <c r="R64" s="99" t="n"/>
+      <c r="S64" s="99" t="n"/>
+    </row>
+    <row r="65" ht="36" customHeight="1" s="84">
+      <c r="A65" s="100" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="B65" s="100" t="inlineStr">
+        <is>
+          <t>Specialty Cheese</t>
+        </is>
+      </c>
+      <c r="C65" s="101" t="inlineStr">
+        <is>
+          <t>Feta Cheese Crumbles</t>
+        </is>
+      </c>
+      <c r="D65" s="101" t="inlineStr">
+        <is>
+          <t>Goat Cheese Logs</t>
+        </is>
+      </c>
+      <c r="E65" s="101" t="n"/>
+      <c r="F65" s="101" t="n"/>
+      <c r="G65" s="101" t="n"/>
+      <c r="H65" s="101" t="n"/>
+      <c r="I65" s="101" t="n"/>
+      <c r="J65" s="101" t="n"/>
+      <c r="K65" s="101" t="n"/>
+      <c r="L65" s="101" t="n"/>
+      <c r="M65" s="101" t="n"/>
+      <c r="N65" s="101" t="n"/>
+      <c r="O65" s="101" t="n"/>
+      <c r="P65" s="101" t="n"/>
+      <c r="Q65" s="101" t="n"/>
+      <c r="R65" s="101" t="n"/>
+      <c r="S65" s="101" t="n"/>
+    </row>
+    <row r="66" ht="36" customHeight="1" s="84">
+      <c r="A66" s="102" t="inlineStr">
+        <is>
+          <t>Toiletries, Cleaning and Disposables</t>
+        </is>
+      </c>
+      <c r="B66" s="102" t="inlineStr">
+        <is>
+          <t>Storage &amp; Organization</t>
+        </is>
+      </c>
+      <c r="C66" s="103" t="inlineStr">
+        <is>
+          <t>Collapsible Storage Container/Bin</t>
+        </is>
+      </c>
+      <c r="D66" s="103" t="n"/>
+      <c r="E66" s="103" t="n"/>
+      <c r="F66" s="103" t="n"/>
+      <c r="G66" s="103" t="n"/>
+      <c r="H66" s="103" t="n"/>
+      <c r="I66" s="103" t="n"/>
+      <c r="J66" s="103" t="n"/>
+      <c r="K66" s="103" t="n"/>
+      <c r="L66" s="103" t="n"/>
+      <c r="M66" s="103" t="n"/>
+      <c r="N66" s="103" t="n"/>
+      <c r="O66" s="103" t="n"/>
+      <c r="P66" s="103" t="n"/>
+      <c r="Q66" s="103" t="n"/>
+      <c r="R66" s="103" t="n"/>
+      <c r="S66" s="103" t="n"/>
+    </row>
+    <row r="67" ht="36" customHeight="1" s="84">
+      <c r="A67" s="104" t="inlineStr">
+        <is>
+          <t>Wine</t>
+        </is>
+      </c>
+      <c r="B67" s="104" t="inlineStr">
+        <is>
+          <t>Wine</t>
+        </is>
+      </c>
+      <c r="C67" s="105" t="inlineStr">
+        <is>
+          <t>Häagen-Dazs Blackberry Ice Cream</t>
+        </is>
+      </c>
+      <c r="D67" s="105" t="inlineStr">
+        <is>
+          <t>Magen David Blackberry Wine</t>
+        </is>
+      </c>
+      <c r="E67" s="105" t="n"/>
+      <c r="F67" s="105" t="n"/>
+      <c r="G67" s="105" t="n"/>
+      <c r="H67" s="105" t="n"/>
+      <c r="I67" s="105" t="n"/>
+      <c r="J67" s="105" t="n"/>
+      <c r="K67" s="105" t="n"/>
+      <c r="L67" s="105" t="n"/>
+      <c r="M67" s="105" t="n"/>
+      <c r="N67" s="105" t="n"/>
+      <c r="O67" s="105" t="n"/>
+      <c r="P67" s="105" t="n"/>
+      <c r="Q67" s="105" t="n"/>
+      <c r="R67" s="105" t="n"/>
+      <c r="S67" s="105" t="n"/>
+    </row>
+    <row r="68" ht="36" customHeight="1" s="84">
+      <c r="A68" s="94" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="B68" s="94" t="inlineStr">
+        <is>
+          <t>Writing Supplies</t>
+        </is>
+      </c>
+      <c r="C68" s="95" t="inlineStr">
+        <is>
+          <t>Gel Pens, 3-Pack</t>
+        </is>
+      </c>
+      <c r="D68" s="95" t="n"/>
+      <c r="E68" s="95" t="n"/>
+      <c r="F68" s="95" t="n"/>
+      <c r="G68" s="95" t="n"/>
+      <c r="H68" s="95" t="n"/>
+      <c r="I68" s="95" t="n"/>
+      <c r="J68" s="95" t="n"/>
+      <c r="K68" s="95" t="n"/>
+      <c r="L68" s="95" t="n"/>
+      <c r="M68" s="95" t="n"/>
+      <c r="N68" s="95" t="n"/>
+      <c r="O68" s="95" t="n"/>
+      <c r="P68" s="95" t="n"/>
+      <c r="Q68" s="95" t="n"/>
+      <c r="R68" s="95" t="n"/>
+      <c r="S68" s="95" t="n"/>
+    </row>
+    <row r="69" ht="36" customHeight="1" s="84">
+      <c r="A69" s="96" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="B69" s="96" t="inlineStr">
+        <is>
+          <t>Yogurt</t>
+        </is>
+      </c>
+      <c r="C69" s="97" t="inlineStr">
+        <is>
+          <t>Chobani Greek Yogurt 4-Pack, Hero Batch</t>
+        </is>
+      </c>
+      <c r="D69" s="97" t="inlineStr">
+        <is>
+          <t>Chobani Protein Greek Yogurt Drink, Strawberries &amp; Cream</t>
+        </is>
+      </c>
+      <c r="E69" s="97" t="inlineStr">
+        <is>
+          <t>Chobani Vanilla Mixed Berry Greek Yogurt</t>
+        </is>
+      </c>
+      <c r="F69" s="97" t="inlineStr">
+        <is>
+          <t>Stonyfield Organic YoBaby Yogurt Pouch, Banana</t>
+        </is>
+      </c>
+      <c r="G69" s="97" t="inlineStr">
+        <is>
+          <t>Stonyfield Organic YoBaby Yogurt Pouch, Peach</t>
+        </is>
+      </c>
+      <c r="H69" s="97" t="n"/>
+      <c r="I69" s="97" t="n"/>
+      <c r="J69" s="97" t="n"/>
+      <c r="K69" s="97" t="n"/>
+      <c r="L69" s="97" t="n"/>
+      <c r="M69" s="97" t="n"/>
+      <c r="N69" s="97" t="n"/>
+      <c r="O69" s="97" t="n"/>
+      <c r="P69" s="97" t="n"/>
+      <c r="Q69" s="97" t="n"/>
+      <c r="R69" s="97" t="n"/>
+      <c r="S69" s="97" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P64"/>
+  <autoFilter ref="A1:S69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25888,9 +28896,9 @@
     </row>
   </sheetData>
   <mergeCells count="281">
+    <mergeCell ref="S207:V207"/>
     <mergeCell ref="S118:V118"/>
     <mergeCell ref="Y113:AG113"/>
-    <mergeCell ref="S207:V207"/>
     <mergeCell ref="S158:V158"/>
     <mergeCell ref="S329:V329"/>
     <mergeCell ref="S210:V210"/>
@@ -25956,8 +28964,8 @@
     <mergeCell ref="Y133:AG133"/>
     <mergeCell ref="Y59:AG62"/>
     <mergeCell ref="Y127:AG127"/>
+    <mergeCell ref="S317:V317"/>
     <mergeCell ref="S204:V204"/>
-    <mergeCell ref="S317:V317"/>
     <mergeCell ref="S99:V99"/>
     <mergeCell ref="S335:V335"/>
     <mergeCell ref="S151:V151"/>
@@ -25978,9 +28986,9 @@
     <mergeCell ref="S76:V76"/>
     <mergeCell ref="S85:V85"/>
     <mergeCell ref="S256:V256"/>
+    <mergeCell ref="S183:V183"/>
     <mergeCell ref="S296:V296"/>
     <mergeCell ref="S94:V94"/>
-    <mergeCell ref="S183:V183"/>
     <mergeCell ref="S75:V75"/>
     <mergeCell ref="S311:V311"/>
     <mergeCell ref="S109:V109"/>
@@ -26027,10 +29035,10 @@
     <mergeCell ref="S10:V10"/>
     <mergeCell ref="S195:V195"/>
     <mergeCell ref="S308:V308"/>
+    <mergeCell ref="S260:V260"/>
     <mergeCell ref="Y290:AG290"/>
     <mergeCell ref="S89:V89"/>
     <mergeCell ref="Y232:AG232"/>
-    <mergeCell ref="S260:V260"/>
     <mergeCell ref="S65:V65"/>
     <mergeCell ref="S74:V74"/>
     <mergeCell ref="S157:V157"/>
@@ -26111,10 +29119,10 @@
     <mergeCell ref="S64:V64"/>
     <mergeCell ref="S104:V104"/>
     <mergeCell ref="S162:V162"/>
+    <mergeCell ref="S340:V340"/>
+    <mergeCell ref="S355:V355"/>
+    <mergeCell ref="Y170:AG173"/>
     <mergeCell ref="S227:V227"/>
-    <mergeCell ref="S355:V355"/>
-    <mergeCell ref="S340:V340"/>
-    <mergeCell ref="Y170:AG173"/>
     <mergeCell ref="S54:V54"/>
     <mergeCell ref="Q218:W218"/>
     <mergeCell ref="Y293:AG296"/>
@@ -26159,14 +29167,14 @@
     <mergeCell ref="Y274:AG274"/>
     <mergeCell ref="S224:V224"/>
     <mergeCell ref="S304:V304"/>
+    <mergeCell ref="Y128:AG131"/>
     <mergeCell ref="S116:V116"/>
-    <mergeCell ref="Y128:AG131"/>
     <mergeCell ref="Y58:AG58"/>
     <mergeCell ref="S352:V352"/>
+    <mergeCell ref="S152:V152"/>
     <mergeCell ref="S196:V196"/>
     <mergeCell ref="S68:V68"/>
     <mergeCell ref="S103:V103"/>
-    <mergeCell ref="S152:V152"/>
     <mergeCell ref="S171:V171"/>
     <mergeCell ref="S84:V84"/>
   </mergeCells>
@@ -30807,8 +33815,8 @@
     <mergeCell ref="Y11:AG14"/>
     <mergeCell ref="S57:V57"/>
     <mergeCell ref="Y152:AG152"/>
+    <mergeCell ref="Y59:AG62"/>
     <mergeCell ref="S229:V229"/>
-    <mergeCell ref="Y59:AG62"/>
     <mergeCell ref="Y239:AG242"/>
     <mergeCell ref="S83:V83"/>
     <mergeCell ref="Y95:AG98"/>
@@ -30840,8 +33848,8 @@
     <mergeCell ref="S10:V10"/>
     <mergeCell ref="Y118:AG118"/>
     <mergeCell ref="Y155:AG158"/>
+    <mergeCell ref="S137:V137"/>
     <mergeCell ref="S195:V195"/>
-    <mergeCell ref="S137:V137"/>
     <mergeCell ref="Y232:AG232"/>
     <mergeCell ref="Q80:W80"/>
     <mergeCell ref="S65:V65"/>
@@ -30849,8 +33857,8 @@
     <mergeCell ref="S157:V157"/>
     <mergeCell ref="S237:V237"/>
     <mergeCell ref="Y22:AG22"/>
+    <mergeCell ref="Y101:AG104"/>
     <mergeCell ref="S129:V129"/>
-    <mergeCell ref="Y101:AG104"/>
     <mergeCell ref="S123:V123"/>
     <mergeCell ref="S138:V138"/>
     <mergeCell ref="S50:V50"/>
@@ -30865,8 +33873,8 @@
     <mergeCell ref="Y47:AG50"/>
     <mergeCell ref="S232:V232"/>
     <mergeCell ref="Y136:AG136"/>
+    <mergeCell ref="Y167:AG170"/>
     <mergeCell ref="S155:V155"/>
-    <mergeCell ref="Y167:AG170"/>
     <mergeCell ref="S52:V52"/>
     <mergeCell ref="Q8:W8"/>
     <mergeCell ref="S86:V86"/>
@@ -32034,32 +35042,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="84" min="1" max="1"/>
     <col width="16" customWidth="1" style="84" min="2" max="3"/>
-    <col width="16" customWidth="1" style="84" min="3" max="3"/>
     <col width="22" customWidth="1" style="84" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="107" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Source OCR JSON</t>
         </is>
       </c>
-      <c r="B1" s="107" t="inlineStr">
+      <c r="B1" s="69" t="inlineStr">
         <is>
           <t>Store Number</t>
         </is>
       </c>
-      <c r="C1" s="107" t="inlineStr">
+      <c r="C1" s="69" t="inlineStr">
         <is>
           <t>Receipt Date</t>
         </is>
       </c>
-      <c r="D1" s="107" t="inlineStr">
+      <c r="D1" s="69" t="inlineStr">
         <is>
           <t>Imported Timestamp</t>
         </is>
@@ -32313,7 +35320,7 @@
       <c r="C15" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="D15" s="134" t="n">
+      <c r="D15" s="3" t="n">
         <v>46271.6522190625</v>
       </c>
     </row>
@@ -32331,8 +35338,62 @@
       <c r="C16" s="2" t="n">
         <v>46271</v>
       </c>
-      <c r="D16" s="134" t="n">
-        <v>46271.65845203114</v>
+      <c r="D16" s="3" t="n">
+        <v>46271.65845202546</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>090626_ALDI_238_C_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>46271.66306559028</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>090726_TraderJoes_0848_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>46272.80318711806</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>090726_TraderJoes_0848_raw_ocr.json</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0848</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>46272.81057715278</v>
       </c>
     </row>
   </sheetData>
@@ -32346,7 +35407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:F8"/>
+  <dimension ref="A4:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15.33203125" bestFit="1" customWidth="1" style="84" min="2" max="2"/>
@@ -32360,20 +35421,30 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>Category Manager Row</t>
+          <t>Excel Row</t>
         </is>
       </c>
       <c r="B4" s="26" t="inlineStr">
         <is>
-          <t>Sub-Category</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="C4" s="26" t="inlineStr">
         <is>
-          <t>New Category</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>New Common Name</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>New Sub-Category</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -32381,83 +35452,241 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coffee Creamer</t>
+          <t>Trader Joe's</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>TAQUITOS BLACK BEAN &amp; CH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Existing ShopGraph taxonomy already places Cream &amp; Half-and-Half, Milk, Plant-Based Milk, Plant-Based Cheese, Specialty Cheese, and Yogurt under Dairy; the Starbucks oatmilk creamer is the same general refrigerated dairy/alternative-dairy purchasing domain.</t>
-        </is>
-      </c>
-      <c r="E5" s="26" t="n"/>
-      <c r="F5" s="26" t="n"/>
+          <t>Black Bean &amp; Cheese Taquitos</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Frozen Appetizers</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Taquitos are a distinct frozen prepared snack/appetizer type not adequately represented by the historical taxonomy, so a new granular Sub-Category is warranted.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1" s="84">
       <c r="A6" t="n">
-        <v>30</v>
+        <v>177</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frozen Desserts</t>
+          <t>Trader Joe's</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>EMPIRE KOSHER TRKY HALF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The products are Klondike and Yasso frozen dessert bars, making Dessert a better semantic fit than the general Frozen/Frozen Food categories; ShopGraph already uses Dessert for other sweet dessert-oriented Sub-Categories.</t>
+          <t>Empire Kosher Turkey Half</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Historical Trader Joe's Empire Kosher turkey is classified as Fresh Poultry, providing strong same-brand/product-family precedent.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rice Cakes &amp; Crisps</t>
+          <t>Trader Joe's</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pantry</t>
+          <t>EMPIRE KOSHER BNL/SKNL B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Quaker Rice Crisps are packaged shelf-stable snack products, aligning with existing Pantry classifications such as Crackers, Popcorn, Snack Bars, Rice &amp; Grains, and similar dry goods.</t>
+          <t>Empire Kosher Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fresh Poultry</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The abbreviation identifies an Empire Kosher boneless/skinless poultry product; Fresh Poultry is already established for fresh kosher poultry rather than the provisional broad Meat &amp; Seafood.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smoked Seafood</t>
+          <t>Trader Joe's</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>BEEF KOSHER GROUND 85/15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ShopGraph already maps Fresh Seafood → Fish; smoked salmon remains the same seafood purchasing domain, so reusing Fish preserves the existing broad taxonomy.</t>
+          <t>Kosher Ground Beef 85/15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fresh Beef</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fresh ground beef is materially different from the existing Deli Meat, Hot Dogs &amp; Sausages, Frozen Meat, and Fresh Poultry classifications, so Fresh Beef adds useful product-type specificity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>180</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CHOCOLATE BABKA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chocolate Babka</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Muffins &amp; Pastries</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Babka is a sweet baked pastry/bread product and fits the existing Muffins &amp; Pastries taxonomy more closely than ordinary Bread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>181</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R-SALAD COMPLETE SWEET K</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Complete Sweet Kale Salad Kit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Salad Kits</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The receipt abbreviation indicates a complete Sweet Kale salad; ShopGraph already uses Salad Kits for comparable complete/chopped salad products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>182</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HALF MOON COOKIES</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Half Moon Cookies</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cookies</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cookies are a distinct product type not represented by an existing dedicated historical Sub-Category, so a new Cookies classification is appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>183</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trader Joe's</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HOL PUMPKIN CREAM CHEESE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pumpkin Cream Cheese</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cream Cheese</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cream cheese is materially distinct from standard Cheese and Specialty Cheese and is specific enough to support a reusable new Sub-Category.</t>
         </is>
       </c>
     </row>
